--- a/test_notebooks_R/print_04_14_2022.xlsx
+++ b/test_notebooks_R/print_04_14_2022.xlsx
@@ -12,9 +12,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="539">
-  <si>
-    <t xml:space="preserve">FSC-T</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="531">
+  <si>
+    <t xml:space="preserve">FSC-T (Week 4 - 04_14_2022)</t>
   </si>
   <si>
     <t xml:space="preserve">Amato, Susan</t>
@@ -458,7 +458,7 @@
     <t xml:space="preserve">5x1 Each Donation to Food Pantry</t>
   </si>
   <si>
-    <t xml:space="preserve">FSD</t>
+    <t xml:space="preserve">FSD (Week 4 - 04_14_2022)</t>
   </si>
   <si>
     <t xml:space="preserve">Carpenter, Rachael</t>
@@ -746,7 +746,7 @@
     <t xml:space="preserve">1x1 Large Horseradish Root</t>
   </si>
   <si>
-    <t xml:space="preserve">FSE</t>
+    <t xml:space="preserve">FSE (Week 4 - 04_14_2022)</t>
   </si>
   <si>
     <t xml:space="preserve">Holzum, Nichole</t>
@@ -968,61 +968,46 @@
     <t xml:space="preserve">1x1 Bottle Thyme for Garlic Vinaigrette</t>
   </si>
   <si>
-    <t xml:space="preserve">Duello, Alex</t>
+    <t xml:space="preserve">Garland, Katherine</t>
   </si>
   <si>
     <t xml:space="preserve">Dawson, Jeff</t>
   </si>
   <si>
+    <t xml:space="preserve">🧀[1]1x1 Each Raw Milk Aged Cheddar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🐄[*]3x64 Ounce Whole MILK-e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Griffin, Barbara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1x1 Each Field to Fire Option</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1x1 Pack Salame - Veneto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kinman, Tricia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lai, Austin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peeler, Michelle</t>
+  </si>
+  <si>
     <t xml:space="preserve">1 No Produce - Order Only (even wk)</t>
   </si>
   <si>
-    <t xml:space="preserve">🧀[1]1x1 Each Raw Milk Aged Cheddar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Garland, Katherine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">🐄[*]3x64 Ounce Whole MILK-e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1x1 Pack Salame - Veneto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Griffin, Barbara</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Horn, maggie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kinman, Tricia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1x1 Each Field to Fire Option</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kelrick, Michael</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Novalis, Christine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lai, Austin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rothgangel, Ella</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peeler, Michelle</t>
-  </si>
-  <si>
     <t xml:space="preserve">2x1 Lb. Radishes - Watermelon</t>
   </si>
   <si>
     <t xml:space="preserve">2x1 Bag Romaine Lettuce - Loose</t>
   </si>
   <si>
-    <t xml:space="preserve">FSG-Thu</t>
+    <t xml:space="preserve">FSG-Thu (Week 4 - 04_14_2022)</t>
   </si>
   <si>
     <t xml:space="preserve">Rainey, Karen</t>
@@ -1085,7 +1070,7 @@
     <t xml:space="preserve">🌱5x1 Pot Pre-ordered Plants</t>
   </si>
   <si>
-    <t xml:space="preserve">FSMini-t</t>
+    <t xml:space="preserve">FSMini-t (Week 4 - 04_14_2022)</t>
   </si>
   <si>
     <t xml:space="preserve">Heidenheimer, Eileen</t>
@@ -1286,7 +1271,7 @@
     <t xml:space="preserve">t- Vanhooser, Sarah</t>
   </si>
   <si>
-    <t xml:space="preserve">KWA</t>
+    <t xml:space="preserve">KWA (Week 4 - 04_14_2022)</t>
   </si>
   <si>
     <t xml:space="preserve">Arbanas, Michael</t>
@@ -1460,7 +1445,7 @@
     <t xml:space="preserve">2x1 Each Granola Bar</t>
   </si>
   <si>
-    <t xml:space="preserve">KWB</t>
+    <t xml:space="preserve">KWB (Week 4 - 04_14_2022)</t>
   </si>
   <si>
     <t xml:space="preserve">Alexander, Sophia</t>
@@ -1487,12 +1472,6 @@
     <t xml:space="preserve">1x1 Bottle RL Chocolate Milk</t>
   </si>
   <si>
-    <t xml:space="preserve">Guevara, Shannon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Graff, Jeff</t>
-  </si>
-  <si>
     <t xml:space="preserve">Hamper, Laura</t>
   </si>
   <si>
@@ -1538,19 +1517,25 @@
     <t xml:space="preserve">Kreienkamp, Charli</t>
   </si>
   <si>
-    <t xml:space="preserve">Nonnenkamp, Donna</t>
+    <t xml:space="preserve">Senne, Jessica</t>
   </si>
   <si>
     <t xml:space="preserve">🐄[*]2x64 Ounce Whole MILK-e</t>
   </si>
   <si>
+    <t xml:space="preserve">1x16 Ounce Cream pint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4x1 Dozen Eggs - BW</t>
+  </si>
+  <si>
     <t xml:space="preserve">Thomas, Ryan</t>
   </si>
   <si>
-    <t xml:space="preserve">4x1 Dozen Eggs - BW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senne, Jessica</t>
+    <t xml:space="preserve">1x1 Lb. Pork - Chop bone-in CB /lb.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wippermann, Jennifer</t>
   </si>
   <si>
     <t xml:space="preserve">1x12 Oz. Goshen Colombia</t>
@@ -1559,19 +1544,10 @@
     <t xml:space="preserve">1x1 Bag Goshen Guatemala</t>
   </si>
   <si>
-    <t xml:space="preserve">1x16 Ounce Cream pint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1x1 Lb. Pork - Chop bone-in CB /lb.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wippermann, Jennifer</t>
-  </si>
-  <si>
     <t xml:space="preserve">1x1 Tub FF Dish - Cheesy Polenta</t>
   </si>
   <si>
-    <t xml:space="preserve">KWM</t>
+    <t xml:space="preserve">KWM (Week 4 - 04_14_2022)</t>
   </si>
   <si>
     <t xml:space="preserve">Austin, Anne</t>
@@ -5418,37 +5394,37 @@
         <v>319</v>
       </c>
       <c r="B492" t="s">
-        <v>320</v>
+        <v>247</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="s">
         <v>247</v>
       </c>
-      <c r="B493"/>
+      <c r="B493" s="2" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="s">
+        <v>320</v>
+      </c>
+      <c r="B494" t="s">
         <v>321</v>
-      </c>
-      <c r="B494" s="1" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="s">
         <v>58</v>
       </c>
-      <c r="B495" t="s">
-        <v>247</v>
-      </c>
+      <c r="B495"/>
     </row>
     <row r="496">
       <c r="A496" t="s">
         <v>29</v>
       </c>
-      <c r="B496" s="2" t="s">
-        <v>135</v>
+      <c r="B496" s="1" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="497">
@@ -5456,44 +5432,58 @@
         <v>57</v>
       </c>
       <c r="B497" t="s">
-        <v>323</v>
+        <v>247</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="s">
         <v>12</v>
       </c>
-      <c r="B498"/>
+      <c r="B498" t="s">
+        <v>305</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="s">
         <v>22</v>
       </c>
-      <c r="B499"/>
+      <c r="B499" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="s">
         <v>252</v>
       </c>
-      <c r="B500"/>
+      <c r="B500" t="s">
+        <v>323</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="s">
         <v>324</v>
       </c>
-      <c r="B501"/>
+      <c r="B501" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502"/>
-      <c r="B502"/>
+      <c r="B502" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503"/>
-      <c r="B503"/>
+      <c r="B503" t="s">
+        <v>252</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504"/>
-      <c r="B504"/>
+      <c r="B504" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505"/>
@@ -5524,137 +5514,103 @@
         <v>247</v>
       </c>
       <c r="B509" t="s">
-        <v>320</v>
+        <v>247</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="s">
-        <v>305</v>
-      </c>
-      <c r="B510"/>
+        <v>29</v>
+      </c>
+      <c r="B510" s="2" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="s">
-        <v>29</v>
-      </c>
-      <c r="B511" s="1" t="s">
-        <v>327</v>
-      </c>
+        <v>323</v>
+      </c>
+      <c r="B511"/>
     </row>
     <row r="512">
       <c r="A512" t="s">
-        <v>328</v>
-      </c>
-      <c r="B512" t="s">
-        <v>247</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="B512"/>
     </row>
     <row r="513">
       <c r="A513" t="s">
-        <v>12</v>
-      </c>
-      <c r="B513" t="s">
-        <v>29</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="B513"/>
     </row>
     <row r="514">
       <c r="A514" t="s">
-        <v>22</v>
-      </c>
-      <c r="B514" t="s">
+        <v>252</v>
+      </c>
+      <c r="B514"/>
+    </row>
+    <row r="515">
+      <c r="A515"/>
+      <c r="B515"/>
+    </row>
+    <row r="516">
+      <c r="A516" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B516"/>
+    </row>
+    <row r="517">
+      <c r="A517" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="515">
-      <c r="A515" t="s">
-        <v>252</v>
-      </c>
-      <c r="B515" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="516">
-      <c r="A516" t="s">
-        <v>15</v>
-      </c>
-      <c r="B516" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="517">
-      <c r="A517"/>
-      <c r="B517" t="s">
-        <v>252</v>
-      </c>
+      <c r="B517"/>
     </row>
     <row r="518">
-      <c r="A518" s="1" t="s">
+      <c r="A518" t="s">
         <v>329</v>
       </c>
       <c r="B518"/>
     </row>
     <row r="519">
       <c r="A519" t="s">
-        <v>320</v>
-      </c>
-      <c r="B519" s="1" t="s">
         <v>330</v>
       </c>
+      <c r="B519"/>
     </row>
     <row r="520">
       <c r="A520"/>
-      <c r="B520" t="s">
-        <v>320</v>
-      </c>
+      <c r="B520"/>
     </row>
     <row r="521">
-      <c r="A521" s="1" t="s">
-        <v>331</v>
-      </c>
+      <c r="A521"/>
       <c r="B521"/>
     </row>
     <row r="522">
-      <c r="A522" t="s">
-        <v>247</v>
-      </c>
-      <c r="B522" s="1" t="s">
-        <v>332</v>
-      </c>
+      <c r="A522"/>
+      <c r="B522"/>
     </row>
     <row r="523">
-      <c r="A523" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="B523" t="s">
-        <v>320</v>
-      </c>
+      <c r="A523"/>
+      <c r="B523"/>
     </row>
     <row r="524">
       <c r="A524"/>
       <c r="B524"/>
     </row>
     <row r="525">
-      <c r="A525" s="1" t="s">
-        <v>333</v>
-      </c>
+      <c r="A525"/>
       <c r="B525"/>
     </row>
     <row r="526">
-      <c r="A526" t="s">
-        <v>320</v>
-      </c>
+      <c r="A526"/>
       <c r="B526"/>
     </row>
     <row r="527">
-      <c r="A527" t="s">
-        <v>334</v>
-      </c>
+      <c r="A527"/>
       <c r="B527"/>
     </row>
     <row r="528">
-      <c r="A528" t="s">
-        <v>335</v>
-      </c>
+      <c r="A528"/>
       <c r="B528"/>
     </row>
     <row r="529">
@@ -5755,18 +5711,18 @@
     </row>
     <row r="553">
       <c r="A553" s="1" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="B553" s="1" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" s="1" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="B554" s="1" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
     </row>
     <row r="555">
@@ -5779,7 +5735,7 @@
     </row>
     <row r="556">
       <c r="A556" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="B556" t="s">
         <v>58</v>
@@ -5793,10 +5749,10 @@
     </row>
     <row r="558">
       <c r="A558" s="1" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="B558" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
     </row>
     <row r="559">
@@ -5807,23 +5763,23 @@
     </row>
     <row r="560">
       <c r="A560" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="B560" s="1" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="B561" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="B562" t="s">
         <v>58</v>
@@ -5839,21 +5795,21 @@
     </row>
     <row r="564">
       <c r="A564" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="B564" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
     </row>
     <row r="565">
       <c r="A565"/>
       <c r="B565" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" s="1" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="B566" t="s">
         <v>9</v>
@@ -5864,7 +5820,7 @@
         <v>29</v>
       </c>
       <c r="B567" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
     </row>
     <row r="568">
@@ -5872,12 +5828,12 @@
         <v>57</v>
       </c>
       <c r="B568" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="B569"/>
     </row>
@@ -5886,12 +5842,12 @@
         <v>50</v>
       </c>
       <c r="B570" s="1" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="B571" t="s">
         <v>309</v>
@@ -5902,7 +5858,7 @@
         <v>217</v>
       </c>
       <c r="B572" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
     </row>
     <row r="573">
@@ -6011,26 +5967,26 @@
     </row>
     <row r="599">
       <c r="A599" s="1" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="B599" s="1" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" s="1" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="B600" s="1" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="B601" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
     </row>
     <row r="602">
@@ -6062,7 +6018,7 @@
         <v>32</v>
       </c>
       <c r="B605" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
     </row>
     <row r="606">
@@ -6070,7 +6026,7 @@
         <v>91</v>
       </c>
       <c r="B606" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
     </row>
     <row r="607">
@@ -6079,18 +6035,18 @@
     </row>
     <row r="608">
       <c r="A608" s="1" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="B608" s="1" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="B609" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
     </row>
     <row r="610">
@@ -6103,7 +6059,7 @@
     </row>
     <row r="611">
       <c r="A611" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="B611" t="s">
         <v>129</v>
@@ -6111,7 +6067,7 @@
     </row>
     <row r="612">
       <c r="A612" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="B612" t="s">
         <v>29</v>
@@ -6119,10 +6075,10 @@
     </row>
     <row r="613">
       <c r="A613" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="B613" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
     </row>
     <row r="614">
@@ -6136,18 +6092,18 @@
         <v>7</v>
       </c>
       <c r="B615" s="1" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
     </row>
     <row r="616">
       <c r="A616"/>
       <c r="B616" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" s="1" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="B617" s="3" t="s">
         <v>69</v>
@@ -6155,10 +6111,10 @@
     </row>
     <row r="618">
       <c r="A618" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="B618" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
     </row>
     <row r="619">
@@ -6171,7 +6127,7 @@
     </row>
     <row r="620">
       <c r="A620" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="B620" t="s">
         <v>29</v>
@@ -6182,12 +6138,12 @@
         <v>292</v>
       </c>
       <c r="B621" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="B622" t="s">
         <v>243</v>
@@ -6195,27 +6151,27 @@
     </row>
     <row r="623">
       <c r="A623" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="B623"/>
     </row>
     <row r="624">
       <c r="A624" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="B624" s="1" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
     </row>
     <row r="625">
       <c r="A625"/>
       <c r="B625" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" s="1" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="B626" s="3" t="s">
         <v>95</v>
@@ -6223,10 +6179,10 @@
     </row>
     <row r="627">
       <c r="A627" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="B627" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
     </row>
     <row r="628">
@@ -6242,27 +6198,27 @@
         <v>135</v>
       </c>
       <c r="B629" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
     </row>
     <row r="630">
       <c r="A630"/>
       <c r="B630" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" s="1" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="B631"/>
     </row>
     <row r="632">
       <c r="A632" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="B632" s="1" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
     </row>
     <row r="633">
@@ -6270,12 +6226,12 @@
         <v>95</v>
       </c>
       <c r="B633" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="B634" s="3" t="s">
         <v>95</v>
@@ -6283,10 +6239,10 @@
     </row>
     <row r="635">
       <c r="A635" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="B635" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
     </row>
     <row r="636">
@@ -6294,12 +6250,12 @@
         <v>90</v>
       </c>
       <c r="B636" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="B637" t="s">
         <v>48</v>
@@ -6337,26 +6293,26 @@
     </row>
     <row r="645">
       <c r="A645" s="1" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="B645" s="1" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" s="1" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="B646" s="1" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="B647" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
     </row>
     <row r="648">
@@ -6369,7 +6325,7 @@
     </row>
     <row r="649">
       <c r="A649" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="B649" t="s">
         <v>29</v>
@@ -6377,7 +6333,7 @@
     </row>
     <row r="650">
       <c r="A650" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="B650" t="s">
         <v>65</v>
@@ -6385,10 +6341,10 @@
     </row>
     <row r="651">
       <c r="A651" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="B651" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
     </row>
     <row r="652">
@@ -6399,16 +6355,16 @@
     </row>
     <row r="653">
       <c r="A653" s="1" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B653"/>
     </row>
     <row r="654">
       <c r="A654" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="B654" s="1" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
     </row>
     <row r="655">
@@ -6416,7 +6372,7 @@
         <v>105</v>
       </c>
       <c r="B655" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
     </row>
     <row r="656">
@@ -6429,10 +6385,10 @@
     </row>
     <row r="657">
       <c r="A657" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="B657" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
     </row>
     <row r="658">
@@ -6445,7 +6401,7 @@
     </row>
     <row r="659">
       <c r="A659" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="B659" t="s">
         <v>296</v>
@@ -6454,12 +6410,12 @@
     <row r="660">
       <c r="A660"/>
       <c r="B660" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" s="1" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="B661" t="s">
         <v>147</v>
@@ -6467,29 +6423,29 @@
     </row>
     <row r="662">
       <c r="A662" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="B662"/>
     </row>
     <row r="663">
       <c r="A663" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="B663" s="1" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="B664" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="B665" t="s">
         <v>97</v>
@@ -6497,7 +6453,7 @@
     </row>
     <row r="666">
       <c r="A666" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="B666" t="s">
         <v>29</v>
@@ -6506,12 +6462,12 @@
     <row r="667">
       <c r="A667"/>
       <c r="B667" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" s="1" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="B668" t="s">
         <v>264</v>
@@ -6519,7 +6475,7 @@
     </row>
     <row r="669">
       <c r="A669" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="B669"/>
     </row>
@@ -6528,18 +6484,18 @@
         <v>135</v>
       </c>
       <c r="B670" s="1" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
     </row>
     <row r="671">
       <c r="A671"/>
       <c r="B671" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" s="1" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="B672" t="s">
         <v>285</v>
@@ -6547,7 +6503,7 @@
     </row>
     <row r="673">
       <c r="A673" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="B673" t="s">
         <v>86</v>
@@ -6555,10 +6511,10 @@
     </row>
     <row r="674">
       <c r="A674" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="B674" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
     </row>
     <row r="675">
@@ -6566,12 +6522,12 @@
         <v>29</v>
       </c>
       <c r="B675" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="B676" t="s">
         <v>110</v>
@@ -6579,7 +6535,7 @@
     </row>
     <row r="677">
       <c r="A677" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="B677" t="s">
         <v>205</v>
@@ -6587,27 +6543,27 @@
     </row>
     <row r="678">
       <c r="A678" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="B678"/>
     </row>
     <row r="679">
       <c r="A679"/>
       <c r="B679" s="1" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" s="1" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="B680" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="B681" s="2" t="s">
         <v>135</v>
@@ -6622,20 +6578,20 @@
     <row r="683">
       <c r="A683"/>
       <c r="B683" s="1" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" s="1" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="B684" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="B685" s="2" t="s">
         <v>135</v>
@@ -6665,31 +6621,31 @@
     </row>
     <row r="691">
       <c r="A691" s="1" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="B691" s="1" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" s="1" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="B692" s="1" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="B693" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B694" t="s">
         <v>56</v>
@@ -6697,7 +6653,7 @@
     </row>
     <row r="695">
       <c r="A695" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="B695" t="s">
         <v>58</v>
@@ -6705,7 +6661,7 @@
     </row>
     <row r="696">
       <c r="A696" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="B696" t="s">
         <v>29</v>
@@ -6727,7 +6683,7 @@
     </row>
     <row r="699">
       <c r="A699" s="1" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="B699" t="s">
         <v>9</v>
@@ -6735,7 +6691,7 @@
     </row>
     <row r="700">
       <c r="A700" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="B700" t="s">
         <v>91</v>
@@ -6743,7 +6699,7 @@
     </row>
     <row r="701">
       <c r="A701" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="B701"/>
     </row>
@@ -6752,20 +6708,20 @@
         <v>29</v>
       </c>
       <c r="B702" s="1" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="B703" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="B704" s="2" t="s">
         <v>135</v>
@@ -6780,20 +6736,20 @@
     <row r="706">
       <c r="A706"/>
       <c r="B706" s="1" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
     </row>
     <row r="707">
       <c r="A707" s="1" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="B707" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
     </row>
     <row r="708">
       <c r="A708" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="B708" s="2" t="s">
         <v>135</v>
@@ -6915,39 +6871,39 @@
     </row>
     <row r="737">
       <c r="A737" s="1" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="B737" s="1" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
     </row>
     <row r="738">
       <c r="A738" s="1" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="B738" s="1" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
     </row>
     <row r="739">
       <c r="A739" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="B739" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
     </row>
     <row r="740">
       <c r="A740" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="B740" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
     </row>
     <row r="741">
       <c r="A741" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="B741" t="s">
         <v>287</v>
@@ -6958,7 +6914,7 @@
         <v>287</v>
       </c>
       <c r="B742" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
     </row>
     <row r="743">
@@ -6966,7 +6922,7 @@
         <v>58</v>
       </c>
       <c r="B743" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
     </row>
     <row r="744">
@@ -6974,7 +6930,7 @@
         <v>208</v>
       </c>
       <c r="B744" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
     </row>
     <row r="745">
@@ -6994,28 +6950,28 @@
     <row r="747">
       <c r="A747"/>
       <c r="B747" s="1" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
     </row>
     <row r="748">
       <c r="A748" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="B748" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
     </row>
     <row r="749">
       <c r="A749" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="B749" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
     </row>
     <row r="750">
       <c r="A750" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="B750" t="s">
         <v>287</v>
@@ -7023,7 +6979,7 @@
     </row>
     <row r="751">
       <c r="A751" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="B751" t="s">
         <v>243</v>
@@ -7031,10 +6987,10 @@
     </row>
     <row r="752">
       <c r="A752" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="B752" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
     </row>
     <row r="753">
@@ -7047,10 +7003,10 @@
     </row>
     <row r="754">
       <c r="A754" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="B754" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
     </row>
     <row r="755">
@@ -7069,10 +7025,10 @@
     </row>
     <row r="757">
       <c r="A757" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="B757" s="1" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
     </row>
     <row r="758">
@@ -7080,7 +7036,7 @@
         <v>96</v>
       </c>
       <c r="B758" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
     </row>
     <row r="759">
@@ -7088,7 +7044,7 @@
         <v>165</v>
       </c>
       <c r="B759" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
     </row>
     <row r="760">
@@ -7099,7 +7055,7 @@
     </row>
     <row r="761">
       <c r="A761" s="1" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="B761" t="s">
         <v>58</v>
@@ -7107,23 +7063,23 @@
     </row>
     <row r="762">
       <c r="A762" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="B762" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
     </row>
     <row r="763">
       <c r="A763" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="B763" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
     </row>
     <row r="764">
       <c r="A764" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="B764" t="s">
         <v>7</v>
@@ -7140,15 +7096,15 @@
         <v>165</v>
       </c>
       <c r="B766" s="1" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
     </row>
     <row r="767">
       <c r="A767" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="B767" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
     </row>
     <row r="768">
@@ -7156,7 +7112,7 @@
         <v>46</v>
       </c>
       <c r="B768" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
     </row>
     <row r="769">
@@ -7167,7 +7123,7 @@
     </row>
     <row r="770">
       <c r="A770" s="1" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="B770" t="s">
         <v>65</v>
@@ -7175,7 +7131,7 @@
     </row>
     <row r="771">
       <c r="A771" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="B771" t="s">
         <v>196</v>
@@ -7183,19 +7139,19 @@
     </row>
     <row r="772">
       <c r="A772" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="B772"/>
     </row>
     <row r="773">
       <c r="A773" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="B773"/>
     </row>
     <row r="774">
       <c r="A774" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="B774"/>
     </row>
@@ -7207,7 +7163,7 @@
     </row>
     <row r="776">
       <c r="A776" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="B776"/>
     </row>
@@ -7237,34 +7193,34 @@
     </row>
     <row r="783">
       <c r="A783" s="1" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="B783" s="1" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
     </row>
     <row r="784">
       <c r="A784" s="1" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="B784" s="1" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
     </row>
     <row r="785">
       <c r="A785" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="B785" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
     </row>
     <row r="786">
       <c r="A786" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="B786" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
     </row>
     <row r="787">
@@ -7277,18 +7233,18 @@
     </row>
     <row r="788">
       <c r="A788" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="B788" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
     </row>
     <row r="789">
       <c r="A789" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="B789" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
     </row>
     <row r="790">
@@ -7304,12 +7260,12 @@
         <v>315</v>
       </c>
       <c r="B791" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
     </row>
     <row r="792">
       <c r="A792" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="B792" t="s">
         <v>299</v>
@@ -7324,28 +7280,28 @@
     <row r="794">
       <c r="A794"/>
       <c r="B794" s="1" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
     </row>
     <row r="795">
       <c r="A795" s="1" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="B795" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
     </row>
     <row r="796">
       <c r="A796" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="B796" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
     </row>
     <row r="797">
       <c r="A797" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="B797" t="s">
         <v>56</v>
@@ -7353,15 +7309,15 @@
     </row>
     <row r="798">
       <c r="A798" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="B798" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
     </row>
     <row r="799">
       <c r="A799" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="B799" t="s">
         <v>109</v>
@@ -7385,7 +7341,7 @@
     </row>
     <row r="802">
       <c r="A802" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="B802" t="s">
         <v>144</v>
@@ -7397,26 +7353,26 @@
     </row>
     <row r="804">
       <c r="A804" s="1" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="B804" s="1" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
     </row>
     <row r="805">
       <c r="A805" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="B805" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
     </row>
     <row r="806">
       <c r="A806" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="B806" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
     </row>
     <row r="807">
@@ -7424,12 +7380,12 @@
         <v>287</v>
       </c>
       <c r="B807" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
     </row>
     <row r="808">
       <c r="A808" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="B808" t="s">
         <v>162</v>
@@ -7437,43 +7393,43 @@
     </row>
     <row r="809">
       <c r="A809" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="B809" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
     </row>
     <row r="810">
       <c r="A810" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="B810"/>
     </row>
     <row r="811">
       <c r="A811" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="B811" s="1" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
     </row>
     <row r="812">
       <c r="A812"/>
       <c r="B812" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
     </row>
     <row r="813">
       <c r="A813" s="1" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="B813" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
     </row>
     <row r="814">
       <c r="A814" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="B814" t="s">
         <v>287</v>
@@ -7484,15 +7440,15 @@
         <v>97</v>
       </c>
       <c r="B815" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
     </row>
     <row r="816">
       <c r="A816" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="B816" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
     </row>
     <row r="817">
@@ -7505,15 +7461,15 @@
     </row>
     <row r="818">
       <c r="A818" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="B818" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
     </row>
     <row r="819">
       <c r="A819" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="B819"/>
     </row>
@@ -7557,42 +7513,42 @@
     </row>
     <row r="829">
       <c r="A829" s="1" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="B829" s="1" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
     </row>
     <row r="830">
       <c r="A830" s="1" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="B830" s="1" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
     </row>
     <row r="831">
       <c r="A831" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="B831" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
     </row>
     <row r="832">
       <c r="A832" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="B832" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
     </row>
     <row r="833">
       <c r="A833" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="B833" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
     </row>
     <row r="834">
@@ -7600,7 +7556,7 @@
         <v>278</v>
       </c>
       <c r="B834" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
     </row>
     <row r="835">
@@ -7616,12 +7572,12 @@
         <v>165</v>
       </c>
       <c r="B836" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
     </row>
     <row r="837">
       <c r="A837" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="B837" t="s">
         <v>49</v>
@@ -7632,7 +7588,7 @@
         <v>70</v>
       </c>
       <c r="B838" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
     </row>
     <row r="839">
@@ -7641,23 +7597,23 @@
     </row>
     <row r="840">
       <c r="A840" s="1" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="B840" s="1" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
     </row>
     <row r="841">
       <c r="A841" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="B841" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
     </row>
     <row r="842">
       <c r="A842" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="B842" t="s">
         <v>313</v>
@@ -7681,7 +7637,7 @@
     </row>
     <row r="845">
       <c r="A845" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="B845" t="s">
         <v>274</v>
@@ -7692,7 +7648,7 @@
         <v>29</v>
       </c>
       <c r="B846" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
     </row>
     <row r="847">
@@ -7700,7 +7656,7 @@
         <v>10</v>
       </c>
       <c r="B847" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
     </row>
     <row r="848">
@@ -7719,7 +7675,7 @@
     </row>
     <row r="850">
       <c r="A850" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="B850"/>
     </row>
@@ -7735,19 +7691,19 @@
     </row>
     <row r="853">
       <c r="A853" s="1" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="B853"/>
     </row>
     <row r="854">
       <c r="A854" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="B854"/>
     </row>
     <row r="855">
       <c r="A855" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="B855"/>
     </row>
@@ -7777,7 +7733,7 @@
     </row>
     <row r="860">
       <c r="A860" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="B860"/>
     </row>
@@ -7847,18 +7803,18 @@
     </row>
     <row r="875">
       <c r="A875" s="1" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="B875" s="1" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
     </row>
     <row r="876">
       <c r="A876" s="1" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="B876" s="1" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
     </row>
     <row r="877">
@@ -7871,18 +7827,18 @@
     </row>
     <row r="878">
       <c r="A878" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="B878" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
     </row>
     <row r="879">
       <c r="A879" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="B879" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
     </row>
     <row r="880">
@@ -7890,7 +7846,7 @@
         <v>58</v>
       </c>
       <c r="B880" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
     </row>
     <row r="881">
@@ -7898,15 +7854,15 @@
         <v>48</v>
       </c>
       <c r="B881" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
     </row>
     <row r="882">
       <c r="A882" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="B882" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
     </row>
     <row r="883">
@@ -7917,263 +7873,255 @@
     </row>
     <row r="884">
       <c r="A884" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="B884" s="1" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
     </row>
     <row r="885">
       <c r="A885"/>
       <c r="B885" t="s">
-        <v>320</v>
+        <v>247</v>
       </c>
     </row>
     <row r="886">
       <c r="A886" s="1" t="s">
-        <v>492</v>
-      </c>
-      <c r="B886"/>
+        <v>487</v>
+      </c>
+      <c r="B886" t="s">
+        <v>472</v>
+      </c>
     </row>
     <row r="887">
       <c r="A887" t="s">
-        <v>320</v>
-      </c>
-      <c r="B887" s="1" t="s">
-        <v>493</v>
+        <v>328</v>
+      </c>
+      <c r="B887" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="888">
-      <c r="A888"/>
+      <c r="A888" t="s">
+        <v>488</v>
+      </c>
       <c r="B888" t="s">
-        <v>247</v>
+        <v>489</v>
       </c>
     </row>
     <row r="889">
-      <c r="A889" s="1" t="s">
-        <v>494</v>
+      <c r="A889" t="s">
+        <v>250</v>
       </c>
       <c r="B889" t="s">
-        <v>477</v>
+        <v>29</v>
       </c>
     </row>
     <row r="890">
       <c r="A890" t="s">
-        <v>320</v>
+        <v>166</v>
       </c>
       <c r="B890" t="s">
-        <v>305</v>
+        <v>490</v>
       </c>
     </row>
     <row r="891">
-      <c r="A891" t="s">
-        <v>495</v>
-      </c>
+      <c r="A891"/>
       <c r="B891" t="s">
-        <v>496</v>
+        <v>12</v>
       </c>
     </row>
     <row r="892">
-      <c r="A892" t="s">
-        <v>250</v>
+      <c r="A892" s="1" t="s">
+        <v>491</v>
       </c>
       <c r="B892" t="s">
-        <v>29</v>
+        <v>492</v>
       </c>
     </row>
     <row r="893">
       <c r="A893" t="s">
-        <v>166</v>
+        <v>247</v>
       </c>
       <c r="B893" t="s">
-        <v>497</v>
+        <v>252</v>
       </c>
     </row>
     <row r="894">
-      <c r="A894"/>
-      <c r="B894" t="s">
-        <v>12</v>
-      </c>
+      <c r="A894" t="s">
+        <v>423</v>
+      </c>
+      <c r="B894"/>
     </row>
     <row r="895">
-      <c r="A895" s="1" t="s">
-        <v>498</v>
-      </c>
-      <c r="B895" t="s">
-        <v>499</v>
+      <c r="A895" t="s">
+        <v>305</v>
+      </c>
+      <c r="B895" s="1" t="s">
+        <v>493</v>
       </c>
     </row>
     <row r="896">
       <c r="A896" t="s">
+        <v>31</v>
+      </c>
+      <c r="B896" t="s">
         <v>247</v>
-      </c>
-      <c r="B896" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="897">
       <c r="A897" t="s">
-        <v>428</v>
-      </c>
-      <c r="B897"/>
+        <v>393</v>
+      </c>
+      <c r="B897" t="s">
+        <v>423</v>
+      </c>
     </row>
     <row r="898">
       <c r="A898" t="s">
-        <v>305</v>
-      </c>
-      <c r="B898" s="1" t="s">
-        <v>500</v>
+        <v>114</v>
+      </c>
+      <c r="B898" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="899">
       <c r="A899" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="B899" t="s">
-        <v>247</v>
+        <v>193</v>
       </c>
     </row>
     <row r="900">
-      <c r="A900" t="s">
-        <v>398</v>
-      </c>
+      <c r="A900"/>
       <c r="B900" t="s">
-        <v>428</v>
+        <v>29</v>
       </c>
     </row>
     <row r="901">
-      <c r="A901" t="s">
-        <v>114</v>
+      <c r="A901" s="1" t="s">
+        <v>494</v>
       </c>
       <c r="B901" t="s">
-        <v>58</v>
+        <v>323</v>
       </c>
     </row>
     <row r="902">
       <c r="A902" t="s">
-        <v>12</v>
+        <v>247</v>
       </c>
       <c r="B902" t="s">
-        <v>193</v>
+        <v>495</v>
       </c>
     </row>
     <row r="903">
-      <c r="A903"/>
+      <c r="A903" t="s">
+        <v>57</v>
+      </c>
       <c r="B903" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
     <row r="904">
-      <c r="A904" s="1" t="s">
-        <v>501</v>
+      <c r="A904" t="s">
+        <v>496</v>
       </c>
       <c r="B904" t="s">
-        <v>328</v>
+        <v>91</v>
       </c>
     </row>
     <row r="905">
       <c r="A905" t="s">
-        <v>247</v>
-      </c>
-      <c r="B905" t="s">
-        <v>502</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="B905"/>
     </row>
     <row r="906">
       <c r="A906" t="s">
-        <v>57</v>
-      </c>
-      <c r="B906" t="s">
-        <v>22</v>
+        <v>50</v>
+      </c>
+      <c r="B906" s="1" t="s">
+        <v>497</v>
       </c>
     </row>
     <row r="907">
       <c r="A907" t="s">
-        <v>503</v>
+        <v>32</v>
       </c>
       <c r="B907" t="s">
-        <v>91</v>
+        <v>247</v>
       </c>
     </row>
     <row r="908">
       <c r="A908" t="s">
-        <v>259</v>
-      </c>
-      <c r="B908"/>
+        <v>498</v>
+      </c>
+      <c r="B908" t="s">
+        <v>472</v>
+      </c>
     </row>
     <row r="909">
       <c r="A909" t="s">
-        <v>50</v>
-      </c>
-      <c r="B909" s="1" t="s">
-        <v>504</v>
+        <v>7</v>
+      </c>
+      <c r="B909" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="910">
       <c r="A910" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="B910" t="s">
-        <v>247</v>
+        <v>8</v>
       </c>
     </row>
     <row r="911">
       <c r="A911" t="s">
-        <v>505</v>
+        <v>347</v>
       </c>
       <c r="B911" t="s">
-        <v>477</v>
+        <v>323</v>
       </c>
     </row>
     <row r="912">
       <c r="A912" t="s">
-        <v>7</v>
+        <v>499</v>
       </c>
       <c r="B912" t="s">
-        <v>58</v>
+        <v>427</v>
       </c>
     </row>
     <row r="913">
-      <c r="A913" t="s">
-        <v>9</v>
-      </c>
+      <c r="A913"/>
       <c r="B913" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="914">
-      <c r="A914" t="s">
-        <v>352</v>
-      </c>
+      <c r="A914"/>
       <c r="B914" t="s">
-        <v>328</v>
+        <v>252</v>
       </c>
     </row>
     <row r="915">
-      <c r="A915" t="s">
-        <v>506</v>
-      </c>
+      <c r="A915"/>
       <c r="B915" t="s">
-        <v>432</v>
+        <v>110</v>
       </c>
     </row>
     <row r="916">
       <c r="A916"/>
-      <c r="B916" t="s">
-        <v>22</v>
-      </c>
+      <c r="B916"/>
     </row>
     <row r="917">
       <c r="A917"/>
-      <c r="B917" t="s">
-        <v>252</v>
-      </c>
+      <c r="B917"/>
     </row>
     <row r="918">
       <c r="A918"/>
-      <c r="B918" t="s">
-        <v>110</v>
-      </c>
+      <c r="B918"/>
     </row>
     <row r="919">
       <c r="A919"/>
@@ -8185,18 +8133,18 @@
     </row>
     <row r="921">
       <c r="A921" s="1" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="B921" s="1" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
     </row>
     <row r="922">
       <c r="A922" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="B922" s="1" t="s">
-        <v>508</v>
+        <v>501</v>
       </c>
     </row>
     <row r="923">
@@ -8204,29 +8152,31 @@
         <v>247</v>
       </c>
       <c r="B923" t="s">
-        <v>320</v>
+        <v>247</v>
       </c>
     </row>
     <row r="924">
       <c r="A924" t="s">
-        <v>509</v>
-      </c>
-      <c r="B924"/>
+        <v>502</v>
+      </c>
+      <c r="B924" t="s">
+        <v>337</v>
+      </c>
     </row>
     <row r="925">
       <c r="A925" t="s">
-        <v>477</v>
-      </c>
-      <c r="B925" s="1" t="s">
-        <v>510</v>
+        <v>472</v>
+      </c>
+      <c r="B925" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="926">
       <c r="A926" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="B926" t="s">
-        <v>247</v>
+        <v>129</v>
       </c>
     </row>
     <row r="927">
@@ -8234,7 +8184,7 @@
         <v>22</v>
       </c>
       <c r="B927" t="s">
-        <v>54</v>
+        <v>360</v>
       </c>
     </row>
     <row r="928">
@@ -8242,37 +8192,37 @@
         <v>263</v>
       </c>
       <c r="B928" t="s">
-        <v>29</v>
+        <v>287</v>
       </c>
     </row>
     <row r="929">
       <c r="A929" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="B929" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
     </row>
     <row r="930">
       <c r="A930" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="B930" t="s">
-        <v>293</v>
+        <v>368</v>
       </c>
     </row>
     <row r="931">
       <c r="A931"/>
       <c r="B931" t="s">
-        <v>328</v>
+        <v>12</v>
       </c>
     </row>
     <row r="932">
       <c r="A932" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="B932" t="s">
-        <v>431</v>
+        <v>22</v>
       </c>
     </row>
     <row r="933">
@@ -8280,129 +8230,123 @@
         <v>247</v>
       </c>
       <c r="B933" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
     </row>
     <row r="934">
       <c r="A934" t="s">
-        <v>342</v>
-      </c>
-      <c r="B934" t="s">
-        <v>514</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="B934"/>
     </row>
     <row r="935">
       <c r="A935" t="s">
-        <v>515</v>
-      </c>
-      <c r="B935" t="s">
-        <v>12</v>
+        <v>29</v>
+      </c>
+      <c r="B935" s="1" t="s">
+        <v>507</v>
       </c>
     </row>
     <row r="936">
       <c r="A936" t="s">
-        <v>129</v>
-      </c>
-      <c r="B936"/>
+        <v>48</v>
+      </c>
+      <c r="B936" t="s">
+        <v>247</v>
+      </c>
     </row>
     <row r="937">
       <c r="A937" t="s">
-        <v>365</v>
-      </c>
-      <c r="B937"/>
+        <v>293</v>
+      </c>
+      <c r="B937" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="938">
       <c r="A938" t="s">
-        <v>287</v>
-      </c>
-      <c r="B938"/>
+        <v>323</v>
+      </c>
+      <c r="B938" t="s">
+        <v>423</v>
+      </c>
     </row>
     <row r="939">
       <c r="A939" t="s">
-        <v>29</v>
-      </c>
-      <c r="B939"/>
+        <v>426</v>
+      </c>
+      <c r="B939" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="940">
       <c r="A940" t="s">
-        <v>373</v>
-      </c>
-      <c r="B940"/>
+        <v>508</v>
+      </c>
+      <c r="B940" t="s">
+        <v>313</v>
+      </c>
     </row>
     <row r="941">
       <c r="A941" t="s">
-        <v>12</v>
-      </c>
-      <c r="B941"/>
+        <v>509</v>
+      </c>
+      <c r="B941" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="942">
       <c r="A942" t="s">
-        <v>22</v>
-      </c>
-      <c r="B942"/>
+        <v>12</v>
+      </c>
+      <c r="B942" t="s">
+        <v>510</v>
+      </c>
     </row>
     <row r="943">
-      <c r="A943" t="s">
-        <v>516</v>
-      </c>
-      <c r="B943"/>
+      <c r="A943"/>
+      <c r="B943" t="s">
+        <v>252</v>
+      </c>
     </row>
     <row r="944">
       <c r="A944"/>
       <c r="B944"/>
     </row>
     <row r="945">
-      <c r="A945" s="1" t="s">
-        <v>517</v>
-      </c>
+      <c r="A945"/>
       <c r="B945"/>
     </row>
     <row r="946">
-      <c r="A946" t="s">
-        <v>247</v>
-      </c>
+      <c r="A946"/>
       <c r="B946"/>
     </row>
     <row r="947">
-      <c r="A947" t="s">
-        <v>137</v>
-      </c>
+      <c r="A947"/>
       <c r="B947"/>
     </row>
     <row r="948">
-      <c r="A948" t="s">
-        <v>428</v>
-      </c>
+      <c r="A948"/>
       <c r="B948"/>
     </row>
     <row r="949">
-      <c r="A949" t="s">
-        <v>54</v>
-      </c>
+      <c r="A949"/>
       <c r="B949"/>
     </row>
     <row r="950">
-      <c r="A950" t="s">
-        <v>313</v>
-      </c>
+      <c r="A950"/>
       <c r="B950"/>
     </row>
     <row r="951">
-      <c r="A951" t="s">
-        <v>31</v>
-      </c>
+      <c r="A951"/>
       <c r="B951"/>
     </row>
     <row r="952">
-      <c r="A952" t="s">
-        <v>518</v>
-      </c>
+      <c r="A952"/>
       <c r="B952"/>
     </row>
     <row r="953">
-      <c r="A953" t="s">
-        <v>252</v>
-      </c>
+      <c r="A953"/>
       <c r="B953"/>
     </row>
     <row r="954">
@@ -8459,31 +8403,31 @@
     </row>
     <row r="967">
       <c r="A967" s="1" t="s">
-        <v>519</v>
+        <v>511</v>
       </c>
       <c r="B967" s="1" t="s">
-        <v>519</v>
+        <v>511</v>
       </c>
     </row>
     <row r="968">
       <c r="A968" s="1" t="s">
-        <v>520</v>
+        <v>512</v>
       </c>
       <c r="B968" s="1" t="s">
-        <v>521</v>
+        <v>513</v>
       </c>
     </row>
     <row r="969">
       <c r="A969" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="B969" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
     </row>
     <row r="970">
       <c r="A970" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="B970" s="2" t="s">
         <v>135</v>
@@ -8491,16 +8435,16 @@
     </row>
     <row r="971">
       <c r="A971" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="B971"/>
     </row>
     <row r="972">
       <c r="A972" t="s">
-        <v>522</v>
+        <v>514</v>
       </c>
       <c r="B972" s="1" t="s">
-        <v>523</v>
+        <v>515</v>
       </c>
     </row>
     <row r="973">
@@ -8508,18 +8452,18 @@
         <v>7</v>
       </c>
       <c r="B973" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
     </row>
     <row r="974">
       <c r="A974"/>
       <c r="B974" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
     </row>
     <row r="975">
       <c r="A975" s="1" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="B975" t="s">
         <v>249</v>
@@ -8527,15 +8471,15 @@
     </row>
     <row r="976">
       <c r="A976" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="B976" t="s">
-        <v>525</v>
+        <v>517</v>
       </c>
     </row>
     <row r="977">
       <c r="A977" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="B977" t="s">
         <v>224</v>
@@ -8551,7 +8495,7 @@
     </row>
     <row r="979">
       <c r="A979" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="B979"/>
     </row>
@@ -8560,7 +8504,7 @@
         <v>8</v>
       </c>
       <c r="B980" s="1" t="s">
-        <v>526</v>
+        <v>518</v>
       </c>
     </row>
     <row r="981">
@@ -8568,12 +8512,12 @@
         <v>29</v>
       </c>
       <c r="B981" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
     </row>
     <row r="982">
       <c r="A982" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="B982" s="2" t="s">
         <v>135</v>
@@ -8585,26 +8529,26 @@
     </row>
     <row r="984">
       <c r="A984" s="1" t="s">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="B984" s="1" t="s">
-        <v>528</v>
+        <v>520</v>
       </c>
     </row>
     <row r="985">
       <c r="A985" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="B985" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
     </row>
     <row r="986">
       <c r="A986" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="B986" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
     </row>
     <row r="987">
@@ -8612,7 +8556,7 @@
         <v>129</v>
       </c>
       <c r="B987" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
     </row>
     <row r="988">
@@ -8620,15 +8564,15 @@
         <v>116</v>
       </c>
       <c r="B988" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
     </row>
     <row r="989">
       <c r="A989" t="s">
-        <v>529</v>
+        <v>521</v>
       </c>
       <c r="B989" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
     </row>
     <row r="990">
@@ -8648,31 +8592,31 @@
     <row r="992">
       <c r="A992"/>
       <c r="B992" s="1" t="s">
-        <v>531</v>
+        <v>523</v>
       </c>
     </row>
     <row r="993">
       <c r="A993" s="1" t="s">
-        <v>532</v>
+        <v>524</v>
       </c>
       <c r="B993" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
     </row>
     <row r="994">
       <c r="A994" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="B994" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
     </row>
     <row r="995">
       <c r="A995" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="B995" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="996">
@@ -8688,20 +8632,20 @@
         <v>29</v>
       </c>
       <c r="B997" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
     </row>
     <row r="998">
       <c r="A998" t="s">
-        <v>534</v>
+        <v>526</v>
       </c>
       <c r="B998" t="s">
-        <v>535</v>
+        <v>527</v>
       </c>
     </row>
     <row r="999">
       <c r="A999" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="B999" t="s">
         <v>193</v>
@@ -8715,7 +8659,7 @@
     </row>
     <row r="1001">
       <c r="A1001" s="1" t="s">
-        <v>537</v>
+        <v>529</v>
       </c>
       <c r="B1001" t="s">
         <v>165</v>
@@ -8723,7 +8667,7 @@
     </row>
     <row r="1002">
       <c r="A1002" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="B1002" t="s">
         <v>205</v>
@@ -8745,13 +8689,13 @@
     </row>
     <row r="1005">
       <c r="A1005" s="1" t="s">
-        <v>538</v>
+        <v>530</v>
       </c>
       <c r="B1005"/>
     </row>
     <row r="1006">
       <c r="A1006" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="B1006"/>
     </row>
@@ -8769,7 +8713,7 @@
     </row>
     <row r="1009">
       <c r="A1009" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="B1009"/>
     </row>
@@ -8789,1008 +8733,968 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A1">
-    <cfRule type="expression" dxfId="0" priority="210">
+    <cfRule type="expression" dxfId="0" priority="202">
       <formula>A1&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:A2">
-    <cfRule type="expression" dxfId="0" priority="209">
+    <cfRule type="expression" dxfId="0" priority="201">
       <formula>A2&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A10:A10">
-    <cfRule type="expression" dxfId="0" priority="208">
+    <cfRule type="expression" dxfId="0" priority="200">
       <formula>A10&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A20:A20">
-    <cfRule type="expression" dxfId="0" priority="207">
+    <cfRule type="expression" dxfId="0" priority="199">
       <formula>A20&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27:A27">
-    <cfRule type="expression" dxfId="0" priority="206">
+    <cfRule type="expression" dxfId="0" priority="198">
       <formula>A27&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A47:A47">
-    <cfRule type="expression" dxfId="0" priority="205">
+    <cfRule type="expression" dxfId="0" priority="197">
       <formula>A47&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A48:A48">
-    <cfRule type="expression" dxfId="0" priority="204">
+    <cfRule type="expression" dxfId="0" priority="196">
       <formula>A48&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A60:A60">
-    <cfRule type="expression" dxfId="0" priority="203">
+    <cfRule type="expression" dxfId="0" priority="195">
       <formula>A60&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A67:A67">
-    <cfRule type="expression" dxfId="0" priority="202">
+    <cfRule type="expression" dxfId="0" priority="194">
       <formula>A67&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A78:A78">
-    <cfRule type="expression" dxfId="0" priority="201">
+    <cfRule type="expression" dxfId="0" priority="193">
       <formula>A78&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A93:A93">
-    <cfRule type="expression" dxfId="0" priority="200">
+    <cfRule type="expression" dxfId="0" priority="192">
       <formula>A93&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A94:A94">
-    <cfRule type="expression" dxfId="0" priority="199">
+    <cfRule type="expression" dxfId="0" priority="191">
       <formula>A94&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A103:A103">
-    <cfRule type="expression" dxfId="0" priority="198">
+    <cfRule type="expression" dxfId="0" priority="190">
       <formula>A103&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A109:A109">
-    <cfRule type="expression" dxfId="0" priority="197">
+    <cfRule type="expression" dxfId="0" priority="189">
       <formula>A109&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A117:A117">
-    <cfRule type="expression" dxfId="0" priority="196">
+    <cfRule type="expression" dxfId="0" priority="188">
       <formula>A117&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A125:A125">
-    <cfRule type="expression" dxfId="0" priority="195">
+    <cfRule type="expression" dxfId="0" priority="187">
       <formula>A125&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A139:A139">
-    <cfRule type="expression" dxfId="0" priority="194">
+    <cfRule type="expression" dxfId="0" priority="186">
       <formula>A139&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A140:A140">
-    <cfRule type="expression" dxfId="0" priority="193">
+    <cfRule type="expression" dxfId="0" priority="185">
       <formula>A140&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A144:A144">
-    <cfRule type="expression" dxfId="0" priority="192">
+    <cfRule type="expression" dxfId="0" priority="184">
       <formula>A144&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A185:A185">
-    <cfRule type="expression" dxfId="1" priority="191">
+    <cfRule type="expression" dxfId="1" priority="183">
       <formula>A185&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A186:A186">
-    <cfRule type="expression" dxfId="1" priority="190">
+    <cfRule type="expression" dxfId="1" priority="182">
       <formula>A186&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A194:A194">
-    <cfRule type="expression" dxfId="1" priority="189">
+    <cfRule type="expression" dxfId="1" priority="181">
       <formula>A194&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A205:A205">
-    <cfRule type="expression" dxfId="1" priority="188">
+    <cfRule type="expression" dxfId="1" priority="180">
       <formula>A205&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A214:A214">
-    <cfRule type="expression" dxfId="1" priority="187">
+    <cfRule type="expression" dxfId="1" priority="179">
       <formula>A214&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A231:A231">
-    <cfRule type="expression" dxfId="1" priority="186">
+    <cfRule type="expression" dxfId="1" priority="178">
       <formula>A231&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A232:A232">
-    <cfRule type="expression" dxfId="1" priority="185">
+    <cfRule type="expression" dxfId="1" priority="177">
       <formula>A232&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A242:A242">
-    <cfRule type="expression" dxfId="1" priority="184">
+    <cfRule type="expression" dxfId="1" priority="176">
       <formula>A242&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A260:A260">
-    <cfRule type="expression" dxfId="1" priority="183">
+    <cfRule type="expression" dxfId="1" priority="175">
       <formula>A260&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A277:A277">
-    <cfRule type="expression" dxfId="1" priority="182">
+    <cfRule type="expression" dxfId="1" priority="174">
       <formula>A277&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A278:A278">
-    <cfRule type="expression" dxfId="1" priority="181">
+    <cfRule type="expression" dxfId="1" priority="173">
       <formula>A278&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A298:A298">
-    <cfRule type="expression" dxfId="1" priority="180">
+    <cfRule type="expression" dxfId="1" priority="172">
       <formula>A298&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A308:A308">
-    <cfRule type="expression" dxfId="1" priority="179">
+    <cfRule type="expression" dxfId="1" priority="171">
       <formula>A308&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A313:A313">
-    <cfRule type="expression" dxfId="1" priority="178">
+    <cfRule type="expression" dxfId="1" priority="170">
       <formula>A313&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A323:A323">
-    <cfRule type="expression" dxfId="1" priority="177">
+    <cfRule type="expression" dxfId="1" priority="169">
       <formula>A323&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A324:A324">
-    <cfRule type="expression" dxfId="1" priority="176">
+    <cfRule type="expression" dxfId="1" priority="168">
       <formula>A324&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A328:A328">
-    <cfRule type="expression" dxfId="1" priority="175">
+    <cfRule type="expression" dxfId="1" priority="167">
       <formula>A328&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A369:A369">
-    <cfRule type="expression" dxfId="2" priority="174">
+    <cfRule type="expression" dxfId="2" priority="166">
       <formula>A369&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A370:A370">
-    <cfRule type="expression" dxfId="2" priority="173">
+    <cfRule type="expression" dxfId="2" priority="165">
       <formula>A370&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A380:A380">
-    <cfRule type="expression" dxfId="2" priority="172">
+    <cfRule type="expression" dxfId="2" priority="164">
       <formula>A380&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A392:A392">
-    <cfRule type="expression" dxfId="2" priority="171">
+    <cfRule type="expression" dxfId="2" priority="163">
       <formula>A392&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A415:A415">
-    <cfRule type="expression" dxfId="2" priority="170">
+    <cfRule type="expression" dxfId="2" priority="162">
       <formula>A415&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A416:A416">
-    <cfRule type="expression" dxfId="2" priority="169">
+    <cfRule type="expression" dxfId="2" priority="161">
       <formula>A416&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A427:A427">
-    <cfRule type="expression" dxfId="2" priority="168">
+    <cfRule type="expression" dxfId="2" priority="160">
       <formula>A427&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A439:A439">
-    <cfRule type="expression" dxfId="2" priority="167">
+    <cfRule type="expression" dxfId="2" priority="159">
       <formula>A439&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A449:A449">
-    <cfRule type="expression" dxfId="2" priority="166">
+    <cfRule type="expression" dxfId="2" priority="158">
       <formula>A449&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A461:A461">
-    <cfRule type="expression" dxfId="2" priority="165">
+    <cfRule type="expression" dxfId="2" priority="157">
       <formula>A461&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A462:A462">
-    <cfRule type="expression" dxfId="2" priority="164">
+    <cfRule type="expression" dxfId="2" priority="156">
       <formula>A462&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A472:A472">
-    <cfRule type="expression" dxfId="2" priority="163">
+    <cfRule type="expression" dxfId="2" priority="155">
       <formula>A472&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A482:A482">
-    <cfRule type="expression" dxfId="2" priority="162">
+    <cfRule type="expression" dxfId="2" priority="154">
       <formula>A482&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A492:A492">
-    <cfRule type="expression" dxfId="2" priority="161">
+    <cfRule type="expression" dxfId="2" priority="153">
       <formula>A492&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A507:A507">
-    <cfRule type="expression" dxfId="2" priority="160">
+    <cfRule type="expression" dxfId="2" priority="152">
       <formula>A507&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A508:A508">
-    <cfRule type="expression" dxfId="2" priority="159">
+    <cfRule type="expression" dxfId="2" priority="151">
       <formula>A508&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A518:A518">
-    <cfRule type="expression" dxfId="2" priority="158">
-      <formula>A518&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A521:A521">
-    <cfRule type="expression" dxfId="2" priority="157">
-      <formula>A521&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A525:A525">
-    <cfRule type="expression" dxfId="2" priority="156">
-      <formula>A525&lt;&gt;0</formula>
+  <conditionalFormatting sqref="A516:A516">
+    <cfRule type="expression" dxfId="2" priority="150">
+      <formula>A516&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A553:A553">
-    <cfRule type="expression" dxfId="3" priority="155">
+    <cfRule type="expression" dxfId="3" priority="149">
       <formula>A553&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A554:A554">
-    <cfRule type="expression" dxfId="3" priority="154">
+    <cfRule type="expression" dxfId="3" priority="148">
       <formula>A554&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A558:A558">
-    <cfRule type="expression" dxfId="3" priority="153">
+    <cfRule type="expression" dxfId="3" priority="147">
       <formula>A558&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A566:A566">
-    <cfRule type="expression" dxfId="3" priority="152">
+    <cfRule type="expression" dxfId="3" priority="146">
       <formula>A566&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A599:A599">
-    <cfRule type="expression" dxfId="4" priority="151">
+    <cfRule type="expression" dxfId="4" priority="145">
       <formula>A599&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A600:A600">
-    <cfRule type="expression" dxfId="4" priority="150">
+    <cfRule type="expression" dxfId="4" priority="144">
       <formula>A600&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A608:A608">
-    <cfRule type="expression" dxfId="4" priority="149">
+    <cfRule type="expression" dxfId="4" priority="143">
       <formula>A608&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A617:A617">
-    <cfRule type="expression" dxfId="4" priority="148">
+    <cfRule type="expression" dxfId="4" priority="142">
       <formula>A617&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A626:A626">
-    <cfRule type="expression" dxfId="4" priority="147">
+    <cfRule type="expression" dxfId="4" priority="141">
       <formula>A626&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A631:A631">
-    <cfRule type="expression" dxfId="4" priority="146">
+    <cfRule type="expression" dxfId="4" priority="140">
       <formula>A631&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A645:A645">
-    <cfRule type="expression" dxfId="4" priority="145">
+    <cfRule type="expression" dxfId="4" priority="139">
       <formula>A645&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A646:A646">
-    <cfRule type="expression" dxfId="4" priority="144">
+    <cfRule type="expression" dxfId="4" priority="138">
       <formula>A646&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A653:A653">
-    <cfRule type="expression" dxfId="4" priority="143">
+    <cfRule type="expression" dxfId="4" priority="137">
       <formula>A653&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A661:A661">
-    <cfRule type="expression" dxfId="4" priority="142">
+    <cfRule type="expression" dxfId="4" priority="136">
       <formula>A661&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A668:A668">
-    <cfRule type="expression" dxfId="4" priority="141">
+    <cfRule type="expression" dxfId="4" priority="135">
       <formula>A668&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A672:A672">
-    <cfRule type="expression" dxfId="4" priority="140">
+    <cfRule type="expression" dxfId="4" priority="134">
       <formula>A672&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A680:A680">
-    <cfRule type="expression" dxfId="4" priority="139">
+    <cfRule type="expression" dxfId="4" priority="133">
       <formula>A680&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A684:A684">
-    <cfRule type="expression" dxfId="4" priority="138">
+    <cfRule type="expression" dxfId="4" priority="132">
       <formula>A684&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A691:A691">
-    <cfRule type="expression" dxfId="4" priority="137">
+    <cfRule type="expression" dxfId="4" priority="131">
       <formula>A691&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A692:A692">
-    <cfRule type="expression" dxfId="4" priority="136">
+    <cfRule type="expression" dxfId="4" priority="130">
       <formula>A692&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A699:A699">
-    <cfRule type="expression" dxfId="4" priority="135">
+    <cfRule type="expression" dxfId="4" priority="129">
       <formula>A699&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A707:A707">
-    <cfRule type="expression" dxfId="4" priority="134">
+    <cfRule type="expression" dxfId="4" priority="128">
       <formula>A707&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A737:A737">
-    <cfRule type="expression" dxfId="5" priority="133">
+    <cfRule type="expression" dxfId="5" priority="127">
       <formula>A737&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A738:A738">
-    <cfRule type="expression" dxfId="5" priority="132">
+    <cfRule type="expression" dxfId="5" priority="126">
       <formula>A738&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A748:A748">
-    <cfRule type="expression" dxfId="5" priority="131">
+    <cfRule type="expression" dxfId="5" priority="125">
       <formula>A748&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A761:A761">
-    <cfRule type="expression" dxfId="5" priority="130">
+    <cfRule type="expression" dxfId="5" priority="124">
       <formula>A761&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A770:A770">
-    <cfRule type="expression" dxfId="5" priority="129">
+    <cfRule type="expression" dxfId="5" priority="123">
       <formula>A770&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A783:A783">
-    <cfRule type="expression" dxfId="5" priority="128">
+    <cfRule type="expression" dxfId="5" priority="122">
       <formula>A783&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A784:A784">
-    <cfRule type="expression" dxfId="5" priority="127">
+    <cfRule type="expression" dxfId="5" priority="121">
       <formula>A784&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A795:A795">
-    <cfRule type="expression" dxfId="5" priority="126">
+    <cfRule type="expression" dxfId="5" priority="120">
       <formula>A795&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A804:A804">
-    <cfRule type="expression" dxfId="5" priority="125">
+    <cfRule type="expression" dxfId="5" priority="119">
       <formula>A804&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A813:A813">
-    <cfRule type="expression" dxfId="5" priority="124">
+    <cfRule type="expression" dxfId="5" priority="118">
       <formula>A813&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A829:A829">
-    <cfRule type="expression" dxfId="5" priority="123">
+    <cfRule type="expression" dxfId="5" priority="117">
       <formula>A829&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A830:A830">
-    <cfRule type="expression" dxfId="5" priority="122">
+    <cfRule type="expression" dxfId="5" priority="116">
       <formula>A830&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A840:A840">
-    <cfRule type="expression" dxfId="5" priority="121">
+    <cfRule type="expression" dxfId="5" priority="115">
       <formula>A840&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A853:A853">
-    <cfRule type="expression" dxfId="5" priority="120">
+    <cfRule type="expression" dxfId="5" priority="114">
       <formula>A853&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A875:A875">
-    <cfRule type="expression" dxfId="6" priority="119">
+    <cfRule type="expression" dxfId="6" priority="113">
       <formula>A875&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A876:A876">
-    <cfRule type="expression" dxfId="6" priority="118">
+    <cfRule type="expression" dxfId="6" priority="112">
       <formula>A876&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A886:A886">
-    <cfRule type="expression" dxfId="6" priority="117">
+    <cfRule type="expression" dxfId="6" priority="111">
       <formula>A886&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A889:A889">
-    <cfRule type="expression" dxfId="6" priority="116">
-      <formula>A889&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A895:A895">
-    <cfRule type="expression" dxfId="6" priority="115">
-      <formula>A895&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A904:A904">
-    <cfRule type="expression" dxfId="6" priority="114">
-      <formula>A904&lt;&gt;0</formula>
+  <conditionalFormatting sqref="A892:A892">
+    <cfRule type="expression" dxfId="6" priority="110">
+      <formula>A892&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A901:A901">
+    <cfRule type="expression" dxfId="6" priority="109">
+      <formula>A901&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A921:A921">
-    <cfRule type="expression" dxfId="6" priority="113">
+    <cfRule type="expression" dxfId="6" priority="108">
       <formula>A921&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A922:A922">
-    <cfRule type="expression" dxfId="6" priority="112">
+    <cfRule type="expression" dxfId="6" priority="107">
       <formula>A922&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A932:A932">
-    <cfRule type="expression" dxfId="6" priority="111">
+    <cfRule type="expression" dxfId="6" priority="106">
       <formula>A932&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A945:A945">
-    <cfRule type="expression" dxfId="6" priority="110">
-      <formula>A945&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="A967:A967">
-    <cfRule type="expression" dxfId="7" priority="109">
+    <cfRule type="expression" dxfId="7" priority="105">
       <formula>A967&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A968:A968">
-    <cfRule type="expression" dxfId="7" priority="108">
+    <cfRule type="expression" dxfId="7" priority="104">
       <formula>A968&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A975:A975">
-    <cfRule type="expression" dxfId="7" priority="107">
+    <cfRule type="expression" dxfId="7" priority="103">
       <formula>A975&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A984:A984">
-    <cfRule type="expression" dxfId="7" priority="106">
+    <cfRule type="expression" dxfId="7" priority="102">
       <formula>A984&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A993:A993">
-    <cfRule type="expression" dxfId="7" priority="105">
+    <cfRule type="expression" dxfId="7" priority="101">
       <formula>A993&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1001:A1001">
-    <cfRule type="expression" dxfId="7" priority="104">
+    <cfRule type="expression" dxfId="7" priority="100">
       <formula>A1001&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1005:A1005">
-    <cfRule type="expression" dxfId="7" priority="103">
+    <cfRule type="expression" dxfId="7" priority="99">
       <formula>A1005&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B1">
-    <cfRule type="expression" dxfId="0" priority="102">
+    <cfRule type="expression" dxfId="0" priority="98">
       <formula>B1&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:B2">
-    <cfRule type="expression" dxfId="0" priority="101">
+    <cfRule type="expression" dxfId="0" priority="97">
       <formula>B2&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:B14">
-    <cfRule type="expression" dxfId="0" priority="100">
+    <cfRule type="expression" dxfId="0" priority="96">
       <formula>B14&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32:B32">
-    <cfRule type="expression" dxfId="0" priority="99">
+    <cfRule type="expression" dxfId="0" priority="95">
       <formula>B32&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B47:B47">
-    <cfRule type="expression" dxfId="0" priority="98">
+    <cfRule type="expression" dxfId="0" priority="94">
       <formula>B47&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B48:B48">
-    <cfRule type="expression" dxfId="0" priority="97">
+    <cfRule type="expression" dxfId="0" priority="93">
       <formula>B48&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B64:B64">
-    <cfRule type="expression" dxfId="0" priority="96">
+    <cfRule type="expression" dxfId="0" priority="92">
       <formula>B64&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B76:B76">
-    <cfRule type="expression" dxfId="0" priority="95">
+    <cfRule type="expression" dxfId="0" priority="91">
       <formula>B76&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B93:B93">
-    <cfRule type="expression" dxfId="0" priority="94">
+    <cfRule type="expression" dxfId="0" priority="90">
       <formula>B93&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B94:B94">
-    <cfRule type="expression" dxfId="0" priority="93">
+    <cfRule type="expression" dxfId="0" priority="89">
       <formula>B94&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B105:B105">
-    <cfRule type="expression" dxfId="0" priority="92">
+    <cfRule type="expression" dxfId="0" priority="88">
       <formula>B105&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B118:B118">
-    <cfRule type="expression" dxfId="0" priority="91">
+    <cfRule type="expression" dxfId="0" priority="87">
       <formula>B118&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B129:B129">
-    <cfRule type="expression" dxfId="0" priority="90">
+    <cfRule type="expression" dxfId="0" priority="86">
       <formula>B129&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B139:B139">
-    <cfRule type="expression" dxfId="0" priority="89">
+    <cfRule type="expression" dxfId="0" priority="85">
       <formula>B139&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B140:B140">
-    <cfRule type="expression" dxfId="0" priority="88">
+    <cfRule type="expression" dxfId="0" priority="84">
       <formula>B140&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B185:B185">
-    <cfRule type="expression" dxfId="1" priority="87">
+    <cfRule type="expression" dxfId="1" priority="83">
       <formula>B185&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B186:B186">
-    <cfRule type="expression" dxfId="1" priority="86">
+    <cfRule type="expression" dxfId="1" priority="82">
       <formula>B186&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B195:B195">
-    <cfRule type="expression" dxfId="1" priority="85">
+    <cfRule type="expression" dxfId="1" priority="81">
       <formula>B195&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B205:B205">
-    <cfRule type="expression" dxfId="1" priority="84">
+    <cfRule type="expression" dxfId="1" priority="80">
       <formula>B205&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B214:B214">
-    <cfRule type="expression" dxfId="1" priority="83">
+    <cfRule type="expression" dxfId="1" priority="79">
       <formula>B214&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B231:B231">
-    <cfRule type="expression" dxfId="1" priority="82">
+    <cfRule type="expression" dxfId="1" priority="78">
       <formula>B231&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B232:B232">
-    <cfRule type="expression" dxfId="1" priority="81">
+    <cfRule type="expression" dxfId="1" priority="77">
       <formula>B232&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B242:B242">
-    <cfRule type="expression" dxfId="1" priority="80">
+    <cfRule type="expression" dxfId="1" priority="76">
       <formula>B242&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B250:B250">
-    <cfRule type="expression" dxfId="1" priority="79">
+    <cfRule type="expression" dxfId="1" priority="75">
       <formula>B250&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B277:B277">
-    <cfRule type="expression" dxfId="1" priority="78">
+    <cfRule type="expression" dxfId="1" priority="74">
       <formula>B277&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B278:B278">
-    <cfRule type="expression" dxfId="1" priority="77">
+    <cfRule type="expression" dxfId="1" priority="73">
       <formula>B278&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B290:B290">
-    <cfRule type="expression" dxfId="1" priority="76">
+    <cfRule type="expression" dxfId="1" priority="72">
       <formula>B290&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B301:B301">
-    <cfRule type="expression" dxfId="1" priority="75">
+    <cfRule type="expression" dxfId="1" priority="71">
       <formula>B301&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B305:B305">
-    <cfRule type="expression" dxfId="1" priority="74">
+    <cfRule type="expression" dxfId="1" priority="70">
       <formula>B305&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B315:B315">
-    <cfRule type="expression" dxfId="1" priority="73">
+    <cfRule type="expression" dxfId="1" priority="69">
       <formula>B315&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B323:B323">
-    <cfRule type="expression" dxfId="1" priority="72">
+    <cfRule type="expression" dxfId="1" priority="68">
       <formula>B323&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B324:B324">
-    <cfRule type="expression" dxfId="1" priority="71">
+    <cfRule type="expression" dxfId="1" priority="67">
       <formula>B324&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B328:B328">
-    <cfRule type="expression" dxfId="1" priority="70">
+    <cfRule type="expression" dxfId="1" priority="66">
       <formula>B328&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B369:B369">
-    <cfRule type="expression" dxfId="2" priority="69">
+    <cfRule type="expression" dxfId="2" priority="65">
       <formula>B369&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B370:B370">
-    <cfRule type="expression" dxfId="2" priority="68">
+    <cfRule type="expression" dxfId="2" priority="64">
       <formula>B370&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B381:B381">
-    <cfRule type="expression" dxfId="2" priority="67">
+    <cfRule type="expression" dxfId="2" priority="63">
       <formula>B381&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B393:B393">
-    <cfRule type="expression" dxfId="2" priority="66">
+    <cfRule type="expression" dxfId="2" priority="62">
       <formula>B393&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B415:B415">
-    <cfRule type="expression" dxfId="2" priority="65">
+    <cfRule type="expression" dxfId="2" priority="61">
       <formula>B415&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B416:B416">
-    <cfRule type="expression" dxfId="2" priority="64">
+    <cfRule type="expression" dxfId="2" priority="60">
       <formula>B416&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B428:B428">
-    <cfRule type="expression" dxfId="2" priority="63">
+    <cfRule type="expression" dxfId="2" priority="59">
       <formula>B428&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B440:B440">
-    <cfRule type="expression" dxfId="2" priority="62">
+    <cfRule type="expression" dxfId="2" priority="58">
       <formula>B440&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B449:B449">
-    <cfRule type="expression" dxfId="2" priority="61">
+    <cfRule type="expression" dxfId="2" priority="57">
       <formula>B449&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B461:B461">
-    <cfRule type="expression" dxfId="2" priority="60">
+    <cfRule type="expression" dxfId="2" priority="56">
       <formula>B461&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B462:B462">
-    <cfRule type="expression" dxfId="2" priority="59">
+    <cfRule type="expression" dxfId="2" priority="55">
       <formula>B462&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B469:B469">
-    <cfRule type="expression" dxfId="2" priority="58">
+    <cfRule type="expression" dxfId="2" priority="54">
       <formula>B469&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B480:B480">
-    <cfRule type="expression" dxfId="2" priority="57">
+    <cfRule type="expression" dxfId="2" priority="53">
       <formula>B480&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B491:B491">
-    <cfRule type="expression" dxfId="2" priority="56">
+    <cfRule type="expression" dxfId="2" priority="52">
       <formula>B491&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B494:B494">
-    <cfRule type="expression" dxfId="2" priority="55">
-      <formula>B494&lt;&gt;0</formula>
+  <conditionalFormatting sqref="B496:B496">
+    <cfRule type="expression" dxfId="2" priority="51">
+      <formula>B496&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B507:B507">
-    <cfRule type="expression" dxfId="2" priority="54">
+    <cfRule type="expression" dxfId="2" priority="50">
       <formula>B507&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B508:B508">
-    <cfRule type="expression" dxfId="2" priority="53">
+    <cfRule type="expression" dxfId="2" priority="49">
       <formula>B508&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B511:B511">
-    <cfRule type="expression" dxfId="2" priority="52">
-      <formula>B511&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B519:B519">
-    <cfRule type="expression" dxfId="2" priority="51">
-      <formula>B519&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B522:B522">
-    <cfRule type="expression" dxfId="2" priority="50">
-      <formula>B522&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B553:B553">
-    <cfRule type="expression" dxfId="3" priority="49">
+    <cfRule type="expression" dxfId="3" priority="48">
       <formula>B553&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B554:B554">
-    <cfRule type="expression" dxfId="3" priority="48">
+    <cfRule type="expression" dxfId="3" priority="47">
       <formula>B554&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B560:B560">
-    <cfRule type="expression" dxfId="3" priority="47">
+    <cfRule type="expression" dxfId="3" priority="46">
       <formula>B560&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B570:B570">
-    <cfRule type="expression" dxfId="3" priority="46">
+    <cfRule type="expression" dxfId="3" priority="45">
       <formula>B570&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B599:B599">
-    <cfRule type="expression" dxfId="4" priority="45">
+    <cfRule type="expression" dxfId="4" priority="44">
       <formula>B599&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B600:B600">
-    <cfRule type="expression" dxfId="4" priority="44">
+    <cfRule type="expression" dxfId="4" priority="43">
       <formula>B600&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B608:B608">
-    <cfRule type="expression" dxfId="4" priority="43">
+    <cfRule type="expression" dxfId="4" priority="42">
       <formula>B608&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B615:B615">
-    <cfRule type="expression" dxfId="4" priority="42">
+    <cfRule type="expression" dxfId="4" priority="41">
       <formula>B615&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B624:B624">
-    <cfRule type="expression" dxfId="4" priority="41">
+    <cfRule type="expression" dxfId="4" priority="40">
       <formula>B624&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B632:B632">
-    <cfRule type="expression" dxfId="4" priority="40">
+    <cfRule type="expression" dxfId="4" priority="39">
       <formula>B632&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B645:B645">
-    <cfRule type="expression" dxfId="4" priority="39">
+    <cfRule type="expression" dxfId="4" priority="38">
       <formula>B645&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B646:B646">
-    <cfRule type="expression" dxfId="4" priority="38">
+    <cfRule type="expression" dxfId="4" priority="37">
       <formula>B646&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B654:B654">
-    <cfRule type="expression" dxfId="4" priority="37">
+    <cfRule type="expression" dxfId="4" priority="36">
       <formula>B654&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B663:B663">
-    <cfRule type="expression" dxfId="4" priority="36">
+    <cfRule type="expression" dxfId="4" priority="35">
       <formula>B663&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B670:B670">
-    <cfRule type="expression" dxfId="4" priority="35">
+    <cfRule type="expression" dxfId="4" priority="34">
       <formula>B670&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B679:B679">
-    <cfRule type="expression" dxfId="4" priority="34">
+    <cfRule type="expression" dxfId="4" priority="33">
       <formula>B679&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B683:B683">
-    <cfRule type="expression" dxfId="4" priority="33">
+    <cfRule type="expression" dxfId="4" priority="32">
       <formula>B683&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B691:B691">
-    <cfRule type="expression" dxfId="4" priority="32">
+    <cfRule type="expression" dxfId="4" priority="31">
       <formula>B691&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B692:B692">
-    <cfRule type="expression" dxfId="4" priority="31">
+    <cfRule type="expression" dxfId="4" priority="30">
       <formula>B692&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B702:B702">
-    <cfRule type="expression" dxfId="4" priority="30">
+    <cfRule type="expression" dxfId="4" priority="29">
       <formula>B702&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B706:B706">
-    <cfRule type="expression" dxfId="4" priority="29">
+    <cfRule type="expression" dxfId="4" priority="28">
       <formula>B706&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B737:B737">
-    <cfRule type="expression" dxfId="5" priority="28">
+    <cfRule type="expression" dxfId="5" priority="27">
       <formula>B737&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B738:B738">
-    <cfRule type="expression" dxfId="5" priority="27">
+    <cfRule type="expression" dxfId="5" priority="26">
       <formula>B738&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B747:B747">
-    <cfRule type="expression" dxfId="5" priority="26">
+    <cfRule type="expression" dxfId="5" priority="25">
       <formula>B747&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B757:B757">
-    <cfRule type="expression" dxfId="5" priority="25">
+    <cfRule type="expression" dxfId="5" priority="24">
       <formula>B757&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B766:B766">
-    <cfRule type="expression" dxfId="5" priority="24">
+    <cfRule type="expression" dxfId="5" priority="23">
       <formula>B766&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B783:B783">
-    <cfRule type="expression" dxfId="5" priority="23">
+    <cfRule type="expression" dxfId="5" priority="22">
       <formula>B783&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B784:B784">
-    <cfRule type="expression" dxfId="5" priority="22">
+    <cfRule type="expression" dxfId="5" priority="21">
       <formula>B784&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B794:B794">
-    <cfRule type="expression" dxfId="5" priority="21">
+    <cfRule type="expression" dxfId="5" priority="20">
       <formula>B794&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B804:B804">
-    <cfRule type="expression" dxfId="5" priority="20">
+    <cfRule type="expression" dxfId="5" priority="19">
       <formula>B804&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B811:B811">
-    <cfRule type="expression" dxfId="5" priority="19">
+    <cfRule type="expression" dxfId="5" priority="18">
       <formula>B811&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B829:B829">
-    <cfRule type="expression" dxfId="5" priority="18">
+    <cfRule type="expression" dxfId="5" priority="17">
       <formula>B829&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B830:B830">
-    <cfRule type="expression" dxfId="5" priority="17">
+    <cfRule type="expression" dxfId="5" priority="16">
       <formula>B830&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B840:B840">
-    <cfRule type="expression" dxfId="5" priority="16">
+    <cfRule type="expression" dxfId="5" priority="15">
       <formula>B840&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B875:B875">
-    <cfRule type="expression" dxfId="6" priority="15">
+    <cfRule type="expression" dxfId="6" priority="14">
       <formula>B875&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B876:B876">
-    <cfRule type="expression" dxfId="6" priority="14">
+    <cfRule type="expression" dxfId="6" priority="13">
       <formula>B876&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B884:B884">
-    <cfRule type="expression" dxfId="6" priority="13">
+    <cfRule type="expression" dxfId="6" priority="12">
       <formula>B884&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B887:B887">
-    <cfRule type="expression" dxfId="6" priority="12">
-      <formula>B887&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B898:B898">
+  <conditionalFormatting sqref="B895:B895">
     <cfRule type="expression" dxfId="6" priority="11">
-      <formula>B898&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B909:B909">
+      <formula>B895&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B906:B906">
     <cfRule type="expression" dxfId="6" priority="10">
-      <formula>B909&lt;&gt;0</formula>
+      <formula>B906&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B921:B921">
@@ -9803,9 +9707,9 @@
       <formula>B922&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B925:B925">
+  <conditionalFormatting sqref="B935:B935">
     <cfRule type="expression" dxfId="6" priority="7">
-      <formula>B925&lt;&gt;0</formula>
+      <formula>B935&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B967:B967">

--- a/test_notebooks_R/print_04_14_2022.xlsx
+++ b/test_notebooks_R/print_04_14_2022.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="531">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="532">
   <si>
     <t xml:space="preserve">FSC-T (Week 4 - 04_14_2022)</t>
   </si>
@@ -53,6 +53,9 @@
     <t xml:space="preserve">1x1 Lb. Ground Beef 80/20</t>
   </si>
   <si>
+    <t xml:space="preserve">NA</t>
+  </si>
+  <si>
     <t xml:space="preserve">1x1 Loaf Seedy Wheaty - Frozen</t>
   </si>
   <si>
@@ -83,7 +86,7 @@
     <t xml:space="preserve">1x1 Choice Mushrooms</t>
   </si>
   <si>
-    <t xml:space="preserve">🐄[*]2x64 Ounce Skim MILK</t>
+    <t xml:space="preserve">➕🐄[*]2x64 Ounce Skim MILK</t>
   </si>
   <si>
     <t xml:space="preserve">1x2 Lb. Rice - White</t>
@@ -107,7 +110,7 @@
     <t xml:space="preserve">1x1 Pint Jam - Black Raspberry HBY</t>
   </si>
   <si>
-    <t xml:space="preserve">2x1 Dozen Eggs</t>
+    <t xml:space="preserve">➕2x1 Dozen Eggs</t>
   </si>
   <si>
     <t xml:space="preserve">1x1 Shiitake Mushrooms</t>
@@ -116,7 +119,7 @@
     <t xml:space="preserve">1x1 Pint RL Heavy Cream</t>
   </si>
   <si>
-    <t xml:space="preserve">🌱8x1 Pot Pre-ordered Plants</t>
+    <t xml:space="preserve">➕🌱8x1 Pot Pre-ordered Plants</t>
   </si>
   <si>
     <t xml:space="preserve">Arnotti, Megan</t>
@@ -131,13 +134,13 @@
     <t xml:space="preserve">🕒1x2 @4-4:30 Mothership Pickup Time</t>
   </si>
   <si>
-    <t xml:space="preserve">🐄[*]2x64 Ounce Whole MILK</t>
+    <t xml:space="preserve">➕🐄[*]2x64 Ounce Whole MILK</t>
   </si>
   <si>
     <t xml:space="preserve">[andouille]1x1 Lb. Pork - Andouille links</t>
   </si>
   <si>
-    <t xml:space="preserve">2x1 lbs Chicken - Thighs /lbs</t>
+    <t xml:space="preserve">➕2x1 lbs Chicken - Thighs /lbs</t>
   </si>
   <si>
     <t xml:space="preserve">Rebe, Jacob</t>
@@ -149,7 +152,7 @@
     <t xml:space="preserve">1x1 Lb. Tortellini - Mushroom</t>
   </si>
   <si>
-    <t xml:space="preserve">🐄[*]2x64 Ounce Creamline MILK</t>
+    <t xml:space="preserve">➕🐄[*]2x64 Ounce Creamline MILK</t>
   </si>
   <si>
     <t xml:space="preserve">1x24 Oz. Yogurt - Greek Plain</t>
@@ -212,7 +215,7 @@
     <t xml:space="preserve">1x1 Loaf Marbled Rye - T</t>
   </si>
   <si>
-    <t xml:space="preserve">🌱3x1 Pot Pre-ordered Plants</t>
+    <t xml:space="preserve">➕🌱3x1 Pot Pre-ordered Plants</t>
   </si>
   <si>
     <t xml:space="preserve">Buckley, Elaine</t>
@@ -230,7 +233,7 @@
     <t xml:space="preserve">1x1 5-pack 80/20 Ground Beef Bundle</t>
   </si>
   <si>
-    <t xml:space="preserve">2x1 Pack Chicken Thighs - Big Bag/lb.</t>
+    <t xml:space="preserve">➕2x1 Pack Chicken Thighs - Big Bag/lb.</t>
   </si>
   <si>
     <t xml:space="preserve">Faust, Thomas</t>
@@ -260,7 +263,7 @@
     <t xml:space="preserve">1x1 Each Pork- Hot Italian Links</t>
   </si>
   <si>
-    <t xml:space="preserve">🌱4x1 Pot Pre-ordered Plants</t>
+    <t xml:space="preserve">➕🌱4x1 Pot Pre-ordered Plants</t>
   </si>
   <si>
     <t xml:space="preserve">🌱1x1 Pot Pre-ordered Plants - cell packs</t>
@@ -380,7 +383,7 @@
     <t xml:space="preserve">1x1 Each Chocolate Gooey Butter Cake</t>
   </si>
   <si>
-    <t xml:space="preserve">🌱9x1 Pot Pre-ordered Plants</t>
+    <t xml:space="preserve">➕🌱9x1 Pot Pre-ordered Plants</t>
   </si>
   <si>
     <t xml:space="preserve">1x1 Lb. Chicken Links - Andouille</t>
@@ -404,7 +407,7 @@
     <t xml:space="preserve">1x1 Each Bacon</t>
   </si>
   <si>
-    <t xml:space="preserve">2x1 Share Shoots - Specialty Mix</t>
+    <t xml:space="preserve">➕2x1 Share Shoots - Specialty Mix</t>
   </si>
   <si>
     <t xml:space="preserve">1x1 Pack Cinnamon Rolls</t>
@@ -455,7 +458,7 @@
     <t xml:space="preserve">1x1 Share Shoots - Specialty Mix</t>
   </si>
   <si>
-    <t xml:space="preserve">5x1 Each Donation to Food Pantry</t>
+    <t xml:space="preserve">➕5x1 Each Donation to Food Pantry</t>
   </si>
   <si>
     <t xml:space="preserve">FSD (Week 4 - 04_14_2022)</t>
@@ -527,13 +530,13 @@
     <t xml:space="preserve">1x1 Quart Buttermilk - Qt.</t>
   </si>
   <si>
-    <t xml:space="preserve">2x1 Each Milk Chocolate Square</t>
+    <t xml:space="preserve">➕2x1 Each Milk Chocolate Square</t>
   </si>
   <si>
     <t xml:space="preserve">1x1 lbs Chuck Roast/lbs.</t>
   </si>
   <si>
-    <t xml:space="preserve">2x1 Loaf Seedy Wheaty Bread</t>
+    <t xml:space="preserve">➕2x1 Loaf Seedy Wheaty Bread</t>
   </si>
   <si>
     <t xml:space="preserve">1x1 Each Pasta - Gluten Free Long LV</t>
@@ -548,13 +551,13 @@
     <t xml:space="preserve">1x1 lbs Leg-o-Lamb - Boneless/lb.</t>
   </si>
   <si>
-    <t xml:space="preserve">🌱18x1 Pot Pre-ordered Plants</t>
+    <t xml:space="preserve">➕🌱18x1 Pot Pre-ordered Plants</t>
   </si>
   <si>
     <t xml:space="preserve">1x1 Bag Buns - John Dough</t>
   </si>
   <si>
-    <t xml:space="preserve">🌱2x1 Pot Pre-ordered Plants - cell packs</t>
+    <t xml:space="preserve">➕🌱2x1 Pot Pre-ordered Plants - cell packs</t>
   </si>
   <si>
     <t xml:space="preserve">1x1 White Pita/Zaatar Bread</t>
@@ -569,10 +572,10 @@
     <t xml:space="preserve">1x1 Each Gift Certificate - 1 full share</t>
   </si>
   <si>
-    <t xml:space="preserve">2x1 Lb. Meatballs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2x1 Jar Tomato Sauce - CB</t>
+    <t xml:space="preserve">➕2x1 Lb. Meatballs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">➕2x1 Jar Tomato Sauce - CB</t>
   </si>
   <si>
     <t xml:space="preserve">1x1 Lb. Red Beets</t>
@@ -590,7 +593,7 @@
     <t xml:space="preserve">Rudy Valli, Valerie</t>
   </si>
   <si>
-    <t xml:space="preserve">🐄[*]5x64 Ounce Whole MILK</t>
+    <t xml:space="preserve">➕🐄[*]5x64 Ounce Whole MILK</t>
   </si>
   <si>
     <t xml:space="preserve">1x1 lbs Chicken Thighs - Boneless/lb.</t>
@@ -614,7 +617,7 @@
     <t xml:space="preserve">1x16 Oz. Almonds - Raw</t>
   </si>
   <si>
-    <t xml:space="preserve">2x1 Pack Ground Turkey</t>
+    <t xml:space="preserve">➕2x1 Pack Ground Turkey</t>
   </si>
   <si>
     <t xml:space="preserve">1x1 Lb. Pork - Deli Ham /lb.</t>
@@ -626,13 +629,13 @@
     <t xml:space="preserve">1x1 Ground Pork - Sweet Italian</t>
   </si>
   <si>
-    <t xml:space="preserve">4x1 Pack Milk Chocolate Bar</t>
+    <t xml:space="preserve">➕4x1 Pack Milk Chocolate Bar</t>
   </si>
   <si>
     <t xml:space="preserve">1x1 Loaf Seedy Wheaty Bread</t>
   </si>
   <si>
-    <t xml:space="preserve">3x1 Package Toffee</t>
+    <t xml:space="preserve">➕3x1 Package Toffee</t>
   </si>
   <si>
     <t xml:space="preserve">Schoen, Heidi</t>
@@ -641,7 +644,7 @@
     <t xml:space="preserve">1x1 Pack Chicken Breasts /lb.</t>
   </si>
   <si>
-    <t xml:space="preserve">2x1 Lion's Mane Mushrooms</t>
+    <t xml:space="preserve">➕2x1 Lion's Mane Mushrooms</t>
   </si>
   <si>
     <t xml:space="preserve">1x2 Lb. Popcorn - McKaskle</t>
@@ -659,7 +662,7 @@
     <t xml:space="preserve">1x1 lbs Flank Steak/lbs.</t>
   </si>
   <si>
-    <t xml:space="preserve">🌱12x1 Pot Pre-ordered Plants</t>
+    <t xml:space="preserve">➕🌱12x1 Pot Pre-ordered Plants</t>
   </si>
   <si>
     <t xml:space="preserve">1x1 Pint Half &amp; Half</t>
@@ -764,7 +767,7 @@
     <t xml:space="preserve">1x1 Each Bada Bing - Sub - Frozen</t>
   </si>
   <si>
-    <t xml:space="preserve">3x1 Dozen Eggs</t>
+    <t xml:space="preserve">➕3x1 Dozen Eggs</t>
   </si>
   <si>
     <t xml:space="preserve">1x1 Pepper Chevre PF</t>
@@ -773,7 +776,7 @@
     <t xml:space="preserve">1x1 Lb. Pasta Long Bi-color</t>
   </si>
   <si>
-    <t xml:space="preserve">3x1 Bottle RL Chocolate Milk</t>
+    <t xml:space="preserve">➕3x1 Bottle RL Chocolate Milk</t>
   </si>
   <si>
     <t xml:space="preserve">1x1 Spicy Pork Snack Sticks - 5 pk</t>
@@ -788,7 +791,7 @@
     <t xml:space="preserve">1x1 Pack Cheddar - Tipsy</t>
   </si>
   <si>
-    <t xml:space="preserve">🐄[*]3x64 Ounce Skim MILK-e</t>
+    <t xml:space="preserve">➕🐄[*]3x64 Ounce Skim MILK-e</t>
   </si>
   <si>
     <t xml:space="preserve">1x1 Jar Honey - Qt.</t>
@@ -845,7 +848,7 @@
     <t xml:space="preserve">Matula, Ashley</t>
   </si>
   <si>
-    <t xml:space="preserve">🐄[*]2x64 Ounce Skim MILK-e</t>
+    <t xml:space="preserve">➕🐄[*]2x64 Ounce Skim MILK-e</t>
   </si>
   <si>
     <t xml:space="preserve">1x1 Mango Curry Sauce</t>
@@ -908,7 +911,7 @@
     <t xml:space="preserve">1x1 Each Salame - Finocchiona</t>
   </si>
   <si>
-    <t xml:space="preserve">2x1 Each Salmon</t>
+    <t xml:space="preserve">➕2x1 Each Salmon</t>
   </si>
   <si>
     <t xml:space="preserve">1x1 Jar Shakshuka Sauce</t>
@@ -944,7 +947,7 @@
     <t xml:space="preserve">1x1 Pack Pork Snack Sticks - Honey 4pk</t>
   </si>
   <si>
-    <t xml:space="preserve">2x1 Each Pork- Hot Italian Links</t>
+    <t xml:space="preserve">➕2x1 Each Pork- Hot Italian Links</t>
   </si>
   <si>
     <t xml:space="preserve">Mayhan, Jessica</t>
@@ -962,7 +965,7 @@
     <t xml:space="preserve">1x1 Quart Jar Tomatoes</t>
   </si>
   <si>
-    <t xml:space="preserve">3x1 Oz. Potato Chips Kickers Mini</t>
+    <t xml:space="preserve">➕3x1 Oz. Potato Chips Kickers Mini</t>
   </si>
   <si>
     <t xml:space="preserve">1x1 Bottle Thyme for Garlic Vinaigrette</t>
@@ -977,7 +980,7 @@
     <t xml:space="preserve">🧀[1]1x1 Each Raw Milk Aged Cheddar</t>
   </si>
   <si>
-    <t xml:space="preserve">🐄[*]3x64 Ounce Whole MILK-e</t>
+    <t xml:space="preserve">➕🐄[*]3x64 Ounce Whole MILK-e</t>
   </si>
   <si>
     <t xml:space="preserve">Griffin, Barbara</t>
@@ -1001,10 +1004,10 @@
     <t xml:space="preserve">1 No Produce - Order Only (even wk)</t>
   </si>
   <si>
-    <t xml:space="preserve">2x1 Lb. Radishes - Watermelon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2x1 Bag Romaine Lettuce - Loose</t>
+    <t xml:space="preserve">➕2x1 Lb. Radishes - Watermelon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">➕2x1 Bag Romaine Lettuce - Loose</t>
   </si>
   <si>
     <t xml:space="preserve">FSG-Thu (Week 4 - 04_14_2022)</t>
@@ -1016,7 +1019,7 @@
     <t xml:space="preserve">Bacher, Blaire</t>
   </si>
   <si>
-    <t xml:space="preserve">4x1 Dozen Eggs</t>
+    <t xml:space="preserve">➕4x1 Dozen Eggs</t>
   </si>
   <si>
     <t xml:space="preserve">Wessels, Chris</t>
@@ -1031,13 +1034,13 @@
     <t xml:space="preserve">Aquilino, Adrian</t>
   </si>
   <si>
-    <t xml:space="preserve">2x1 Lb. Ground Beef 80/20</t>
+    <t xml:space="preserve">➕2x1 Lb. Ground Beef 80/20</t>
   </si>
   <si>
     <t xml:space="preserve">1x1 Bag Brioche - Buns - Frozen</t>
   </si>
   <si>
-    <t xml:space="preserve">2x1 Lb. Ground Beef 90/10</t>
+    <t xml:space="preserve">➕2x1 Lb. Ground Beef 90/10</t>
   </si>
   <si>
     <t xml:space="preserve">1x1 Lb. Pork Chops - Boneless CB /lb.</t>
@@ -1067,7 +1070,7 @@
     <t xml:space="preserve">1x1 Pint Salsa - Gringo's Medium</t>
   </si>
   <si>
-    <t xml:space="preserve">🌱5x1 Pot Pre-ordered Plants</t>
+    <t xml:space="preserve">➕🌱5x1 Pot Pre-ordered Plants</t>
   </si>
   <si>
     <t xml:space="preserve">FSMini-t (Week 4 - 04_14_2022)</t>
@@ -1166,13 +1169,13 @@
     <t xml:space="preserve">1x1 Pack NY Strip Steak /lb</t>
   </si>
   <si>
-    <t xml:space="preserve">🌱10x1 Pot Pre-ordered Plants</t>
+    <t xml:space="preserve">➕🌱10x1 Pot Pre-ordered Plants</t>
   </si>
   <si>
     <t xml:space="preserve">1x12 Oz. Stringbean Peru</t>
   </si>
   <si>
-    <t xml:space="preserve">🌱2x1 Pot Pre-ordered Plants</t>
+    <t xml:space="preserve">➕🌱2x1 Pot Pre-ordered Plants</t>
   </si>
   <si>
     <t xml:space="preserve">Pratt, Angelica</t>
@@ -1226,7 +1229,7 @@
     <t xml:space="preserve">1x1 Pint Peanut Butter MC</t>
   </si>
   <si>
-    <t xml:space="preserve">🌱3x1 Pot Pre-ordered Plants - cell packs</t>
+    <t xml:space="preserve">➕🌱3x1 Pot Pre-ordered Plants - cell packs</t>
   </si>
   <si>
     <t xml:space="preserve">Karr, Mary</t>
@@ -1304,13 +1307,13 @@
     <t xml:space="preserve">Brown, Andrew</t>
   </si>
   <si>
-    <t xml:space="preserve">🐄[*]2x64 Ounce 2% MILK</t>
+    <t xml:space="preserve">➕🐄[*]2x64 Ounce 2% MILK</t>
   </si>
   <si>
     <t xml:space="preserve">1x1 Plain Cheese Curds</t>
   </si>
   <si>
-    <t xml:space="preserve">🌱6x1 Pot Pre-ordered Plants</t>
+    <t xml:space="preserve">➕🌱6x1 Pot Pre-ordered Plants</t>
   </si>
   <si>
     <t xml:space="preserve">Day, April</t>
@@ -1322,7 +1325,7 @@
     <t xml:space="preserve">1x2 Lb. Deli Rye Bread</t>
   </si>
   <si>
-    <t xml:space="preserve">🐄[*]2x64 Oz. Milk - 2%</t>
+    <t xml:space="preserve">➕🐄[*]2x64 Oz. Milk - 2%</t>
   </si>
   <si>
     <t xml:space="preserve">1x1 Bag Pita - White - Frozen</t>
@@ -1334,13 +1337,13 @@
     <t xml:space="preserve">Dziurgot, Rosemary</t>
   </si>
   <si>
-    <t xml:space="preserve">2x1 Pack Beef - Stew Meat</t>
+    <t xml:space="preserve">➕2x1 Pack Beef - Stew Meat</t>
   </si>
   <si>
     <t xml:space="preserve">1x1 Tub Black Bean Hummus</t>
   </si>
   <si>
-    <t xml:space="preserve">2x1 Lb. Carrots</t>
+    <t xml:space="preserve">➕2x1 Lb. Carrots</t>
   </si>
   <si>
     <t xml:space="preserve">Gallup, Kristi</t>
@@ -1373,10 +1376,10 @@
     <t xml:space="preserve">Lampitt, Maggie</t>
   </si>
   <si>
-    <t xml:space="preserve">2x1 Lb. Chicken - Ground</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3x1 Pack Chicken Breasts /lb.</t>
+    <t xml:space="preserve">➕2x1 Lb. Chicken - Ground</t>
+  </si>
+  <si>
+    <t xml:space="preserve">➕3x1 Pack Chicken Breasts /lb.</t>
   </si>
   <si>
     <t xml:space="preserve">1x24 Oz. Yogurt - Vanilla Regular</t>
@@ -1388,7 +1391,7 @@
     <t xml:space="preserve">Novak, Barbara</t>
   </si>
   <si>
-    <t xml:space="preserve">2x1 Pack Chicken Breasts /lb.</t>
+    <t xml:space="preserve">➕2x1 Pack Chicken Breasts /lb.</t>
   </si>
   <si>
     <t xml:space="preserve">1x1 Each Dark Chocolate Square</t>
@@ -1421,7 +1424,7 @@
     <t xml:space="preserve">1x1 Each Baklava</t>
   </si>
   <si>
-    <t xml:space="preserve">2x1 Each Milk Chocolate Lolli</t>
+    <t xml:space="preserve">➕2x1 Each Milk Chocolate Lolli</t>
   </si>
   <si>
     <t xml:space="preserve">Taube, Rachel and Ryan</t>
@@ -1442,7 +1445,7 @@
     <t xml:space="preserve">Wenzel, Ashley</t>
   </si>
   <si>
-    <t xml:space="preserve">2x1 Each Granola Bar</t>
+    <t xml:space="preserve">➕2x1 Each Granola Bar</t>
   </si>
   <si>
     <t xml:space="preserve">KWB (Week 4 - 04_14_2022)</t>
@@ -1463,7 +1466,7 @@
     <t xml:space="preserve">1x1 Each Milk Chocolate Square</t>
   </si>
   <si>
-    <t xml:space="preserve">2x1 Lb. Pork Tenderloin/# - CB</t>
+    <t xml:space="preserve">➕2x1 Lb. Pork Tenderloin/# - CB</t>
   </si>
   <si>
     <t xml:space="preserve">1x1 Spinach Lasagna</t>
@@ -1520,13 +1523,13 @@
     <t xml:space="preserve">Senne, Jessica</t>
   </si>
   <si>
-    <t xml:space="preserve">🐄[*]2x64 Ounce Whole MILK-e</t>
+    <t xml:space="preserve">➕🐄[*]2x64 Ounce Whole MILK-e</t>
   </si>
   <si>
     <t xml:space="preserve">1x16 Ounce Cream pint</t>
   </si>
   <si>
-    <t xml:space="preserve">4x1 Dozen Eggs - BW</t>
+    <t xml:space="preserve">➕4x1 Dozen Eggs - BW</t>
   </si>
   <si>
     <t xml:space="preserve">Thomas, Ryan</t>
@@ -1565,7 +1568,7 @@
     <t xml:space="preserve">Ericson, Rebecca</t>
   </si>
   <si>
-    <t xml:space="preserve">2x1 Pack Croissants</t>
+    <t xml:space="preserve">➕2x1 Pack Croissants</t>
   </si>
   <si>
     <t xml:space="preserve">Noll, Elle</t>
@@ -1577,7 +1580,7 @@
     <t xml:space="preserve">Sears, Anna/Mark</t>
   </si>
   <si>
-    <t xml:space="preserve">2x1 Bottle RL Chocolate Milk</t>
+    <t xml:space="preserve">➕2x1 Bottle RL Chocolate Milk</t>
   </si>
   <si>
     <t xml:space="preserve">1x1 Tub FF Sauce - Mole</t>
@@ -1662,7 +1665,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="9">
     <dxf>
       <font>
         <sz val="12"/>
@@ -1724,7 +1727,7 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FF46BDC6"/>
+          <bgColor rgb="FF5DD6DF"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1766,6 +1769,14 @@
           <bgColor rgb="FFB3EF99"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <b/>
+      </font>
     </dxf>
   </dxfs>
 </styleSheet>
@@ -2122,17 +2133,19 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9"/>
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
@@ -2148,26 +2161,28 @@
         <v>4</v>
       </c>
       <c r="B12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13"/>
+        <v>18</v>
+      </c>
+      <c r="B13" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B15" t="s">
         <v>3</v>
@@ -2175,7 +2190,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>4</v>
@@ -2183,32 +2198,34 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19"/>
+      <c r="A19" t="s">
+        <v>13</v>
+      </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B20" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21">
@@ -2216,7 +2233,7 @@
         <v>3</v>
       </c>
       <c r="B21" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22">
@@ -2224,45 +2241,47 @@
         <v>4</v>
       </c>
       <c r="B22" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B23" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B25" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26"/>
+      <c r="A26" t="s">
+        <v>13</v>
+      </c>
       <c r="B26" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B27" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="28">
@@ -2270,42 +2289,44 @@
         <v>3</v>
       </c>
       <c r="B28" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B29" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B30" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>28</v>
-      </c>
-      <c r="B31"/>
+        <v>29</v>
+      </c>
+      <c r="B31" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B33" t="s">
         <v>3</v>
@@ -2313,7 +2334,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>4</v>
@@ -2321,36 +2342,38 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B35" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B36" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37"/>
+      <c r="A37" t="s">
+        <v>13</v>
+      </c>
       <c r="B37" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="38">
       <c r="A38"/>
       <c r="B38" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="39">
       <c r="A39"/>
       <c r="B39" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="40">
@@ -2362,12 +2385,14 @@
     <row r="41">
       <c r="A41"/>
       <c r="B41" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="42">
       <c r="A42"/>
-      <c r="B42"/>
+      <c r="B42" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43"/>
@@ -2395,10 +2420,10 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="49">
@@ -2411,88 +2436,90 @@
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B51" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B52" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B53" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B54" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B55" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B56" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B57" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B58" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59"/>
+      <c r="A59" t="s">
+        <v>13</v>
+      </c>
       <c r="B59" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B60" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="61">
@@ -2500,51 +2527,55 @@
         <v>3</v>
       </c>
       <c r="B61" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B62" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>71</v>
-      </c>
-      <c r="B63"/>
+        <v>72</v>
+      </c>
+      <c r="B63" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B65" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66"/>
+      <c r="A66" t="s">
+        <v>13</v>
+      </c>
       <c r="B66" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B67" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="68">
@@ -2552,83 +2583,87 @@
         <v>3</v>
       </c>
       <c r="B68" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B70" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B71" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B72" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B73" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B74" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>82</v>
-      </c>
-      <c r="B75"/>
+        <v>83</v>
+      </c>
+      <c r="B75" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77"/>
+      <c r="A77" t="s">
+        <v>13</v>
+      </c>
       <c r="B77" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="79">
@@ -2636,52 +2671,52 @@
         <v>3</v>
       </c>
       <c r="B79" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B80" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B81" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B82" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B84" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B85" t="s">
         <v>11</v>
@@ -2689,12 +2724,16 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>92</v>
-      </c>
-      <c r="B86"/>
+        <v>93</v>
+      </c>
+      <c r="B86" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="87">
-      <c r="A87"/>
+      <c r="A87" t="s">
+        <v>13</v>
+      </c>
       <c r="B87"/>
     </row>
     <row r="88">
@@ -2727,10 +2766,10 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="95">
@@ -2743,83 +2782,87 @@
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B97" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B99" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B100" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B101" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102"/>
+      <c r="A102" t="s">
+        <v>13</v>
+      </c>
       <c r="B102" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B103" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
         <v>3</v>
       </c>
-      <c r="B104"/>
+      <c r="B104" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B106" t="s">
         <v>3</v>
@@ -2827,24 +2870,26 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108"/>
+      <c r="A108" t="s">
+        <v>13</v>
+      </c>
       <c r="B108" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="110">
@@ -2852,72 +2897,76 @@
         <v>3</v>
       </c>
       <c r="B110" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B111" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B112" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B113" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B114" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B115" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="116">
-      <c r="A116"/>
+      <c r="A116" t="s">
+        <v>13</v>
+      </c>
       <c r="B116" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B117"/>
+        <v>113</v>
+      </c>
+      <c r="B117" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
         <v>3</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B119" t="s">
         <v>3</v>
@@ -2925,48 +2974,50 @@
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B121" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B122" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B123" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="124">
-      <c r="A124"/>
+      <c r="A124" t="s">
+        <v>13</v>
+      </c>
       <c r="B124" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B125" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="126">
@@ -2979,29 +3030,31 @@
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B127" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>58</v>
-      </c>
-      <c r="B128"/>
+        <v>59</v>
+      </c>
+      <c r="B128" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B130" t="s">
         <v>3</v>
@@ -3009,38 +3062,40 @@
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B132" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="134">
-      <c r="A134"/>
+      <c r="A134" t="s">
+        <v>13</v>
+      </c>
       <c r="B134" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="135">
       <c r="A135"/>
       <c r="B135" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="136">
@@ -3058,7 +3113,7 @@
     <row r="138">
       <c r="A138"/>
       <c r="B138" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="139">
@@ -3071,10 +3126,10 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="141">
@@ -3087,24 +3142,26 @@
     </row>
     <row r="142">
       <c r="A142" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B142" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="143">
-      <c r="A143"/>
+      <c r="A143" t="s">
+        <v>13</v>
+      </c>
       <c r="B143" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B144" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="145">
@@ -3112,55 +3169,55 @@
         <v>3</v>
       </c>
       <c r="B145" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B146" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B147" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B148" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B149" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B150" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B151" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="152">
@@ -3168,12 +3225,16 @@
         <v>11</v>
       </c>
       <c r="B152" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="153">
-      <c r="A153"/>
-      <c r="B153"/>
+      <c r="A153" t="s">
+        <v>13</v>
+      </c>
+      <c r="B153" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154"/>
@@ -3301,26 +3362,26 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B187" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="188">
@@ -3333,261 +3394,277 @@
     </row>
     <row r="189">
       <c r="A189" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B189" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B190" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B191" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B192" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="193">
-      <c r="A193"/>
+      <c r="A193" t="s">
+        <v>13</v>
+      </c>
       <c r="B193" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="B194"/>
+        <v>158</v>
+      </c>
+      <c r="B194" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B196" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B198" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B199" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B200" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B201" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B202" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B203" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="204">
-      <c r="A204"/>
-      <c r="B204"/>
+      <c r="A204" t="s">
+        <v>13</v>
+      </c>
+      <c r="B204" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B206" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B208" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B209" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B210" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B211" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B212" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="213">
-      <c r="A213"/>
-      <c r="B213"/>
+      <c r="A213" t="s">
+        <v>13</v>
+      </c>
+      <c r="B213" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B215" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B217" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B218" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B219" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="220">
-      <c r="A220"/>
+      <c r="A220" t="s">
+        <v>13</v>
+      </c>
       <c r="B220" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="221">
       <c r="A221"/>
       <c r="B221" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="222">
       <c r="A222"/>
       <c r="B222" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="223">
       <c r="A223"/>
-      <c r="B223"/>
+      <c r="B223" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224"/>
@@ -3619,172 +3696,178 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B233" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B234" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B235" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B236" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B237" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B238" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B239" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B240" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="241">
-      <c r="A241"/>
-      <c r="B241"/>
+      <c r="A241" t="s">
+        <v>13</v>
+      </c>
+      <c r="B241" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B243" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B244" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B245" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B246" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B247" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B248" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="s">
-        <v>58</v>
-      </c>
-      <c r="B249"/>
+        <v>59</v>
+      </c>
+      <c r="B249" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B251" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B252" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="253">
@@ -3792,101 +3875,107 @@
         <v>12</v>
       </c>
       <c r="B253" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B254" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B255" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B256" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B257" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="s">
-        <v>166</v>
-      </c>
-      <c r="B258"/>
+        <v>167</v>
+      </c>
+      <c r="B258" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="259">
-      <c r="A259"/>
+      <c r="A259" t="s">
+        <v>13</v>
+      </c>
       <c r="B259"/>
     </row>
     <row r="260">
       <c r="A260" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B260"/>
     </row>
     <row r="261">
       <c r="A261" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B261"/>
     </row>
     <row r="262">
       <c r="A262" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B262"/>
     </row>
     <row r="263">
       <c r="A263" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B263"/>
     </row>
     <row r="264">
       <c r="A264" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B264"/>
     </row>
     <row r="265">
       <c r="A265" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B265"/>
     </row>
     <row r="266">
       <c r="A266" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B266"/>
     </row>
     <row r="267">
       <c r="A267" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B267"/>
     </row>
     <row r="268">
-      <c r="A268"/>
+      <c r="A268" t="s">
+        <v>13</v>
+      </c>
       <c r="B268"/>
     </row>
     <row r="269">
@@ -3923,136 +4012,138 @@
     </row>
     <row r="277">
       <c r="A277" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B279" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B280" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B281" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B282" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B283" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B284" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B285" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B286" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B287" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B288" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="s">
-        <v>218</v>
-      </c>
-      <c r="B289"/>
+        <v>219</v>
+      </c>
+      <c r="B289" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B291" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B292" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B293" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="294">
@@ -4060,89 +4151,95 @@
         <v>7</v>
       </c>
       <c r="B294" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B295" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B296" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="297">
-      <c r="A297"/>
+      <c r="A297" t="s">
+        <v>13</v>
+      </c>
       <c r="B297" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B298" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B299" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="B300"/>
+        <v>128</v>
+      </c>
+      <c r="B300" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B302" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B303" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="s">
-        <v>65</v>
-      </c>
-      <c r="B304"/>
+        <v>66</v>
+      </c>
+      <c r="B304" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B305" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="306">
@@ -4150,111 +4247,121 @@
         <v>9</v>
       </c>
       <c r="B306" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="307">
-      <c r="A307"/>
+      <c r="A307" t="s">
+        <v>13</v>
+      </c>
       <c r="B307" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B308" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B309" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B310" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B311" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="312">
-      <c r="A312"/>
+      <c r="A312" t="s">
+        <v>13</v>
+      </c>
       <c r="B312" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B313" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="s">
-        <v>151</v>
-      </c>
-      <c r="B314"/>
+        <v>152</v>
+      </c>
+      <c r="B314" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B315" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B316" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B317" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="s">
-        <v>238</v>
-      </c>
-      <c r="B318"/>
+        <v>239</v>
+      </c>
+      <c r="B318" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B319"/>
     </row>
     <row r="320">
       <c r="A320" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B320"/>
     </row>
     <row r="321">
-      <c r="A321"/>
+      <c r="A321" t="s">
+        <v>13</v>
+      </c>
       <c r="B321"/>
     </row>
     <row r="322">
@@ -4263,102 +4370,110 @@
     </row>
     <row r="323">
       <c r="A323" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B323" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B325" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B326" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="327">
-      <c r="A327"/>
-      <c r="B327"/>
+      <c r="A327" t="s">
+        <v>13</v>
+      </c>
+      <c r="B327" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B329" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B330" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="s">
-        <v>141</v>
-      </c>
-      <c r="B331"/>
+        <v>142</v>
+      </c>
+      <c r="B331" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B332"/>
     </row>
     <row r="333">
       <c r="A333" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B333"/>
     </row>
     <row r="334">
       <c r="A334" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B334"/>
     </row>
     <row r="335">
       <c r="A335" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B335"/>
     </row>
     <row r="336">
       <c r="A336" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B336"/>
     </row>
     <row r="337">
-      <c r="A337"/>
+      <c r="A337" t="s">
+        <v>13</v>
+      </c>
       <c r="B337"/>
     </row>
     <row r="338">
@@ -4487,26 +4602,26 @@
     </row>
     <row r="369">
       <c r="A369" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B369" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B370" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B371" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="372">
@@ -4519,26 +4634,26 @@
     </row>
     <row r="373">
       <c r="A373" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B373" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B374" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B375" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="376">
@@ -4546,67 +4661,71 @@
         <v>12</v>
       </c>
       <c r="B376" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B377" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B378" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="379">
-      <c r="A379"/>
+      <c r="A379" t="s">
+        <v>13</v>
+      </c>
       <c r="B379" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="B380"/>
+        <v>256</v>
+      </c>
+      <c r="B380" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B381" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B382" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B383" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B384" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="385">
@@ -4614,39 +4733,39 @@
         <v>8</v>
       </c>
       <c r="B385" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B386" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B387" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B388" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B389" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="390">
@@ -4654,64 +4773,68 @@
         <v>9</v>
       </c>
       <c r="B390" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="391">
-      <c r="A391"/>
+      <c r="A391" t="s">
+        <v>13</v>
+      </c>
       <c r="B391" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="B392"/>
+        <v>261</v>
+      </c>
+      <c r="B392" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B393" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B394" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B395" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B396" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B397" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B398" t="s">
         <v>12</v>
@@ -4719,58 +4842,62 @@
     </row>
     <row r="399">
       <c r="A399" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B399" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B400" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B401" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B402" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B403" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="s">
-        <v>266</v>
-      </c>
-      <c r="B404"/>
+        <v>267</v>
+      </c>
+      <c r="B404" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B405"/>
     </row>
     <row r="406">
-      <c r="A406"/>
+      <c r="A406" t="s">
+        <v>13</v>
+      </c>
       <c r="B406"/>
     </row>
     <row r="407">
@@ -4807,74 +4934,74 @@
     </row>
     <row r="415">
       <c r="A415" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B415" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B416" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B417" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B418" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B419" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B420" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B421" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B422" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B423" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="424">
@@ -4887,70 +5014,74 @@
     </row>
     <row r="425">
       <c r="A425" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B425" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="426">
-      <c r="A426"/>
+      <c r="A426" t="s">
+        <v>13</v>
+      </c>
       <c r="B426" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="B427"/>
+        <v>276</v>
+      </c>
+      <c r="B427" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B428" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B429" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B430" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B431" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B432" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B433" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="434">
@@ -4958,20 +5089,20 @@
         <v>12</v>
       </c>
       <c r="B434" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B435" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B436" t="s">
         <v>12</v>
@@ -4979,151 +5110,159 @@
     </row>
     <row r="437">
       <c r="A437" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B437" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="438">
-      <c r="A438"/>
+      <c r="A438" t="s">
+        <v>13</v>
+      </c>
       <c r="B438" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="B439"/>
+        <v>284</v>
+      </c>
+      <c r="B439" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B440" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B441" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B442" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B443" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B444" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B445" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B446" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B447" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="448">
-      <c r="A448"/>
-      <c r="B448"/>
+      <c r="A448" t="s">
+        <v>13</v>
+      </c>
+      <c r="B448" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B449" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B450" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B451" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B452" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B453" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B454" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B455" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B456" t="s">
         <v>12</v>
@@ -5131,23 +5270,27 @@
     </row>
     <row r="457">
       <c r="A457" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B457" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B458" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="459">
-      <c r="A459"/>
-      <c r="B459"/>
+      <c r="A459" t="s">
+        <v>13</v>
+      </c>
+      <c r="B459" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460"/>
@@ -5155,199 +5298,207 @@
     </row>
     <row r="461">
       <c r="A461" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B461" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B462" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B463" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B464" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B465" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B466" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B467" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="s">
-        <v>298</v>
-      </c>
-      <c r="B468"/>
+        <v>299</v>
+      </c>
+      <c r="B468" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B469" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B470" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="471">
-      <c r="A471"/>
+      <c r="A471" t="s">
+        <v>13</v>
+      </c>
       <c r="B471" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B472" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B473" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B474" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B475" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B476" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B477" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B478" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="s">
-        <v>309</v>
-      </c>
-      <c r="B479"/>
+        <v>310</v>
+      </c>
+      <c r="B479" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B480" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="481">
-      <c r="A481"/>
+      <c r="A481" t="s">
+        <v>13</v>
+      </c>
       <c r="B481" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B482" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B483" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B484" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B485" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B486" t="s">
         <v>12</v>
@@ -5355,84 +5506,90 @@
     </row>
     <row r="487">
       <c r="A487" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B487" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B488" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B489" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="s">
-        <v>317</v>
-      </c>
-      <c r="B490"/>
+        <v>318</v>
+      </c>
+      <c r="B490" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="491">
-      <c r="A491"/>
+      <c r="A491" t="s">
+        <v>13</v>
+      </c>
       <c r="B491" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B492" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B493" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B494" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="s">
-        <v>58</v>
-      </c>
-      <c r="B495"/>
+        <v>59</v>
+      </c>
+      <c r="B495" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B496" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B497" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="498">
@@ -5440,54 +5597,58 @@
         <v>12</v>
       </c>
       <c r="B498" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B499" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B500" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B501" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="502">
-      <c r="A502"/>
+      <c r="A502" t="s">
+        <v>13</v>
+      </c>
       <c r="B502" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="503">
       <c r="A503"/>
       <c r="B503" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="504">
       <c r="A504"/>
       <c r="B504" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="505">
       <c r="A505"/>
-      <c r="B505"/>
+      <c r="B505" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506"/>
@@ -5495,90 +5656,96 @@
     </row>
     <row r="507">
       <c r="A507" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B507" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B508" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B509" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B510" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="s">
-        <v>323</v>
-      </c>
-      <c r="B511"/>
+        <v>324</v>
+      </c>
+      <c r="B511" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B512"/>
     </row>
     <row r="513">
       <c r="A513" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B513"/>
     </row>
     <row r="514">
       <c r="A514" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B514"/>
     </row>
     <row r="515">
-      <c r="A515"/>
+      <c r="A515" t="s">
+        <v>13</v>
+      </c>
       <c r="B515"/>
     </row>
     <row r="516">
       <c r="A516" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B516"/>
     </row>
     <row r="517">
       <c r="A517" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B517"/>
     </row>
     <row r="518">
       <c r="A518" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B518"/>
     </row>
     <row r="519">
       <c r="A519" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B519"/>
     </row>
     <row r="520">
-      <c r="A520"/>
+      <c r="A520" t="s">
+        <v>13</v>
+      </c>
       <c r="B520"/>
     </row>
     <row r="521">
@@ -5711,105 +5878,111 @@
     </row>
     <row r="553">
       <c r="A553" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B553" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B554" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B555" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B556" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="557">
-      <c r="A557"/>
+      <c r="A557" t="s">
+        <v>13</v>
+      </c>
       <c r="B557" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B558" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="B559"/>
+        <v>106</v>
+      </c>
+      <c r="B559" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="560">
       <c r="A560" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B560" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B561" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B562" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B563" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B564" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="565">
-      <c r="A565"/>
+      <c r="A565" t="s">
+        <v>13</v>
+      </c>
       <c r="B565" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B566" t="s">
         <v>9</v>
@@ -5817,53 +5990,59 @@
     </row>
     <row r="567">
       <c r="A567" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B567" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B568" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="s">
-        <v>348</v>
-      </c>
-      <c r="B569"/>
+        <v>349</v>
+      </c>
+      <c r="B569" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="570">
       <c r="A570" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B570" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B571" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B572" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="573">
-      <c r="A573"/>
-      <c r="B573"/>
+      <c r="A573" t="s">
+        <v>13</v>
+      </c>
+      <c r="B573" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="574">
       <c r="A574"/>
@@ -5967,26 +6146,26 @@
     </row>
     <row r="599">
       <c r="A599" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B599" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B600" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B601" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="602">
@@ -5999,54 +6178,58 @@
     </row>
     <row r="603">
       <c r="A603" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B603" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B604" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B605" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B606" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="607">
-      <c r="A607"/>
-      <c r="B607"/>
+      <c r="A607" t="s">
+        <v>13</v>
+      </c>
+      <c r="B607" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="608">
       <c r="A608" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B608" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B609" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="610">
@@ -6054,222 +6237,238 @@
         <v>4</v>
       </c>
       <c r="B610" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B611" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B612" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B613" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="s">
-        <v>110</v>
-      </c>
-      <c r="B614"/>
+        <v>111</v>
+      </c>
+      <c r="B614" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="615">
       <c r="A615" t="s">
         <v>7</v>
       </c>
       <c r="B615" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="616">
-      <c r="A616"/>
+      <c r="A616" t="s">
+        <v>13</v>
+      </c>
       <c r="B616" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B617" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B618" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B619" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B620" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B621" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B622" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="s">
-        <v>370</v>
-      </c>
-      <c r="B623"/>
+        <v>371</v>
+      </c>
+      <c r="B623" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="624">
       <c r="A624" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B624" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="625">
-      <c r="A625"/>
+      <c r="A625" t="s">
+        <v>13</v>
+      </c>
       <c r="B625" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B626" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B627" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B628" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B629" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="630">
-      <c r="A630"/>
+      <c r="A630" t="s">
+        <v>13</v>
+      </c>
       <c r="B630" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="B631"/>
+        <v>376</v>
+      </c>
+      <c r="B631" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="632">
       <c r="A632" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B632" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B633" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B634" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="s">
+        <v>379</v>
+      </c>
+      <c r="B635" t="s">
         <v>378</v>
-      </c>
-      <c r="B635" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B636" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B637" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="638">
-      <c r="A638"/>
+      <c r="A638" t="s">
+        <v>13</v>
+      </c>
       <c r="B638" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="639">
       <c r="A639"/>
-      <c r="B639"/>
+      <c r="B639" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="640">
       <c r="A640"/>
@@ -6293,318 +6492,344 @@
     </row>
     <row r="645">
       <c r="A645" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B645" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B646" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B647" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B648" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B649" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B650" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B651" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="652">
-      <c r="A652"/>
+      <c r="A652" t="s">
+        <v>13</v>
+      </c>
       <c r="B652" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="B653"/>
+        <v>388</v>
+      </c>
+      <c r="B653" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="654">
       <c r="A654" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B654" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B655" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B656" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B657" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B658" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B659" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="660">
-      <c r="A660"/>
+      <c r="A660" t="s">
+        <v>13</v>
+      </c>
       <c r="B660" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B661" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="s">
-        <v>355</v>
-      </c>
-      <c r="B662"/>
+        <v>356</v>
+      </c>
+      <c r="B662" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="663">
       <c r="A663" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B663" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B664" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B665" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B666" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="667">
-      <c r="A667"/>
+      <c r="A667" t="s">
+        <v>13</v>
+      </c>
       <c r="B667" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B668" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="s">
-        <v>355</v>
-      </c>
-      <c r="B669"/>
+        <v>356</v>
+      </c>
+      <c r="B669" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="670">
       <c r="A670" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B670" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="671">
-      <c r="A671"/>
+      <c r="A671" t="s">
+        <v>13</v>
+      </c>
       <c r="B671" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B672" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B673" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B674" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B675" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B676" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B677" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="s">
-        <v>404</v>
-      </c>
-      <c r="B678"/>
+        <v>405</v>
+      </c>
+      <c r="B678" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="679">
-      <c r="A679"/>
+      <c r="A679" t="s">
+        <v>13</v>
+      </c>
       <c r="B679" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B680" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B681" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="B682"/>
+        <v>136</v>
+      </c>
+      <c r="B682" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="683">
-      <c r="A683"/>
+      <c r="A683" t="s">
+        <v>13</v>
+      </c>
       <c r="B683" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B684" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B685" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="B686"/>
+        <v>136</v>
+      </c>
+      <c r="B686" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="687">
-      <c r="A687"/>
+      <c r="A687" t="s">
+        <v>13</v>
+      </c>
       <c r="B687"/>
     </row>
     <row r="688">
@@ -6621,69 +6846,71 @@
     </row>
     <row r="691">
       <c r="A691" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B691" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B692" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B693" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B694" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B695" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B696" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B697" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="698">
-      <c r="A698"/>
+      <c r="A698" t="s">
+        <v>13</v>
+      </c>
       <c r="B698" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B699" t="s">
         <v>9</v>
@@ -6691,78 +6918,88 @@
     </row>
     <row r="700">
       <c r="A700" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B700" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="s">
-        <v>414</v>
-      </c>
-      <c r="B701"/>
+        <v>415</v>
+      </c>
+      <c r="B701" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="702">
       <c r="A702" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B702" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B703" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B704" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="s">
-        <v>68</v>
-      </c>
-      <c r="B705"/>
+        <v>69</v>
+      </c>
+      <c r="B705" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="706">
-      <c r="A706"/>
+      <c r="A706" t="s">
+        <v>13</v>
+      </c>
       <c r="B706" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="707">
       <c r="A707" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B707" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="708">
       <c r="A708" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B708" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="709">
       <c r="A709" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="B709"/>
+        <v>136</v>
+      </c>
+      <c r="B709" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="710">
-      <c r="A710"/>
+      <c r="A710" t="s">
+        <v>13</v>
+      </c>
       <c r="B710"/>
     </row>
     <row r="711">
@@ -6871,215 +7108,223 @@
     </row>
     <row r="737">
       <c r="A737" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B737" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="738">
       <c r="A738" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B738" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="739">
       <c r="A739" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B739" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="740">
       <c r="A740" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B740" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="741">
       <c r="A741" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B741" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="742">
       <c r="A742" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B742" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="743">
       <c r="A743" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B743" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="744">
       <c r="A744" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B744" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="745">
       <c r="A745" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B745" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="746">
       <c r="A746" t="s">
-        <v>196</v>
-      </c>
-      <c r="B746"/>
+        <v>197</v>
+      </c>
+      <c r="B746" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="747">
-      <c r="A747"/>
+      <c r="A747" t="s">
+        <v>13</v>
+      </c>
       <c r="B747" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="748">
       <c r="A748" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B748" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="749">
       <c r="A749" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B749" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="750">
       <c r="A750" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B750" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="751">
       <c r="A751" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B751" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="752">
       <c r="A752" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B752" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="753">
       <c r="A753" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B753" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="754">
       <c r="A754" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B754" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="755">
       <c r="A755" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B755" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="756">
       <c r="A756" t="s">
-        <v>289</v>
-      </c>
-      <c r="B756"/>
+        <v>290</v>
+      </c>
+      <c r="B756" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="757">
       <c r="A757" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B757" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="758">
       <c r="A758" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B758" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="759">
       <c r="A759" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B759" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="760">
-      <c r="A760"/>
+      <c r="A760" t="s">
+        <v>13</v>
+      </c>
       <c r="B760" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="761">
       <c r="A761" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B761" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="762">
       <c r="A762" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B762" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="763">
       <c r="A763" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B763" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="764">
       <c r="A764" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B764" t="s">
         <v>7</v>
@@ -7087,88 +7332,96 @@
     </row>
     <row r="765">
       <c r="A765" t="s">
-        <v>243</v>
-      </c>
-      <c r="B765"/>
+        <v>244</v>
+      </c>
+      <c r="B765" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="766">
       <c r="A766" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B766" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="767">
       <c r="A767" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B767" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="768">
       <c r="A768" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B768" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="769">
-      <c r="A769"/>
+      <c r="A769" t="s">
+        <v>13</v>
+      </c>
       <c r="B769" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="770">
       <c r="A770" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B770" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="771">
       <c r="A771" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B771" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="772">
       <c r="A772" t="s">
-        <v>440</v>
-      </c>
-      <c r="B772"/>
+        <v>441</v>
+      </c>
+      <c r="B772" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="773">
       <c r="A773" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B773"/>
     </row>
     <row r="774">
       <c r="A774" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B774"/>
     </row>
     <row r="775">
       <c r="A775" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B775"/>
     </row>
     <row r="776">
       <c r="A776" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B776"/>
     </row>
     <row r="777">
-      <c r="A777"/>
+      <c r="A777" t="s">
+        <v>13</v>
+      </c>
       <c r="B777"/>
     </row>
     <row r="778">
@@ -7193,294 +7446,310 @@
     </row>
     <row r="783">
       <c r="A783" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B783" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="784">
       <c r="A784" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B784" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="785">
       <c r="A785" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B785" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="786">
       <c r="A786" t="s">
+        <v>425</v>
+      </c>
+      <c r="B786" t="s">
         <v>424</v>
-      </c>
-      <c r="B786" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="787">
       <c r="A787" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B787" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="788">
       <c r="A788" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B788" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="789">
       <c r="A789" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B789" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="790">
       <c r="A790" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B790" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="791">
       <c r="A791" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B791" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="792">
       <c r="A792" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B792" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="793">
       <c r="A793" t="s">
         <v>7</v>
       </c>
-      <c r="B793"/>
+      <c r="B793" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="794">
-      <c r="A794"/>
+      <c r="A794" t="s">
+        <v>13</v>
+      </c>
       <c r="B794" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="795">
       <c r="A795" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B795" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="796">
       <c r="A796" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B796" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="797">
       <c r="A797" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B797" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="798">
       <c r="A798" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B798" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="799">
       <c r="A799" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B799" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="800">
       <c r="A800" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B800" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="801">
       <c r="A801" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B801" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="802">
       <c r="A802" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B802" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="803">
-      <c r="A803"/>
-      <c r="B803"/>
+      <c r="A803" t="s">
+        <v>13</v>
+      </c>
+      <c r="B803" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="804">
       <c r="A804" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B804" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="805">
       <c r="A805" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B805" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="806">
       <c r="A806" t="s">
+        <v>425</v>
+      </c>
+      <c r="B806" t="s">
         <v>424</v>
-      </c>
-      <c r="B806" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="807">
       <c r="A807" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B807" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="808">
       <c r="A808" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B808" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="809">
       <c r="A809" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B809" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="810">
       <c r="A810" t="s">
-        <v>460</v>
-      </c>
-      <c r="B810"/>
+        <v>461</v>
+      </c>
+      <c r="B810" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="811">
       <c r="A811" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B811" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="812">
-      <c r="A812"/>
+      <c r="A812" t="s">
+        <v>13</v>
+      </c>
       <c r="B812" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="813">
       <c r="A813" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B813" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="814">
       <c r="A814" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B814" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="815">
       <c r="A815" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B815" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="816">
       <c r="A816" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B816" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="817">
       <c r="A817" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B817" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="818">
       <c r="A818" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B818" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="819">
       <c r="A819" t="s">
-        <v>450</v>
-      </c>
-      <c r="B819"/>
+        <v>451</v>
+      </c>
+      <c r="B819" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="820">
       <c r="A820" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B820"/>
     </row>
     <row r="821">
-      <c r="A821"/>
+      <c r="A821" t="s">
+        <v>13</v>
+      </c>
       <c r="B821"/>
     </row>
     <row r="822">
@@ -7513,115 +7782,119 @@
     </row>
     <row r="829">
       <c r="A829" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B829" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="830">
       <c r="A830" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B830" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="831">
       <c r="A831" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B831" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="832">
       <c r="A832" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B832" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="833">
       <c r="A833" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B833" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="834">
       <c r="A834" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B834" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="835">
       <c r="A835" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B835" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="836">
       <c r="A836" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B836" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="837">
       <c r="A837" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B837" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="838">
       <c r="A838" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B838" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="839">
-      <c r="A839"/>
-      <c r="B839"/>
+      <c r="A839" t="s">
+        <v>13</v>
+      </c>
+      <c r="B839" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="840">
       <c r="A840" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B840" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="841">
       <c r="A841" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B841" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="842">
       <c r="A842" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B842" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="843">
       <c r="A843" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B843" t="s">
         <v>8</v>
@@ -7629,26 +7902,26 @@
     </row>
     <row r="844">
       <c r="A844" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B844" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="845">
       <c r="A845" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B845" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="846">
       <c r="A846" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B846" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="847">
@@ -7656,54 +7929,58 @@
         <v>10</v>
       </c>
       <c r="B847" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="848">
       <c r="A848" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B848" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="849">
       <c r="A849" t="s">
-        <v>235</v>
-      </c>
-      <c r="B849"/>
+        <v>236</v>
+      </c>
+      <c r="B849" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="850">
       <c r="A850" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B850"/>
     </row>
     <row r="851">
       <c r="A851" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B851"/>
     </row>
     <row r="852">
-      <c r="A852"/>
+      <c r="A852" t="s">
+        <v>13</v>
+      </c>
       <c r="B852"/>
     </row>
     <row r="853">
       <c r="A853" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B853"/>
     </row>
     <row r="854">
       <c r="A854" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B854"/>
     </row>
     <row r="855">
       <c r="A855" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B855"/>
     </row>
@@ -7715,54 +7992,56 @@
     </row>
     <row r="857">
       <c r="A857" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B857"/>
     </row>
     <row r="858">
       <c r="A858" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B858"/>
     </row>
     <row r="859">
       <c r="A859" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B859"/>
     </row>
     <row r="860">
       <c r="A860" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B860"/>
     </row>
     <row r="861">
       <c r="A861" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B861"/>
     </row>
     <row r="862">
       <c r="A862" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B862"/>
     </row>
     <row r="863">
       <c r="A863" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B863"/>
     </row>
     <row r="864">
       <c r="A864" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B864"/>
     </row>
     <row r="865">
-      <c r="A865"/>
+      <c r="A865" t="s">
+        <v>13</v>
+      </c>
       <c r="B865"/>
     </row>
     <row r="866">
@@ -7803,186 +8082,194 @@
     </row>
     <row r="875">
       <c r="A875" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B875" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="876">
       <c r="A876" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B876" s="1" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="877">
       <c r="A877" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B877" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="878">
       <c r="A878" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B878" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="879">
       <c r="A879" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B879" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="880">
       <c r="A880" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B880" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="881">
       <c r="A881" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B881" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="882">
       <c r="A882" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B882" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="883">
       <c r="A883" t="s">
-        <v>115</v>
-      </c>
-      <c r="B883"/>
+        <v>116</v>
+      </c>
+      <c r="B883" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="884">
       <c r="A884" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B884" s="1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="885">
-      <c r="A885"/>
+      <c r="A885" t="s">
+        <v>13</v>
+      </c>
       <c r="B885" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="886">
       <c r="A886" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B886" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="887">
       <c r="A887" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B887" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="888">
       <c r="A888" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B888" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="889">
       <c r="A889" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B889" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="890">
       <c r="A890" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B890" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="891">
-      <c r="A891"/>
+      <c r="A891" t="s">
+        <v>13</v>
+      </c>
       <c r="B891" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="892">
       <c r="A892" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B892" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="893">
       <c r="A893" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B893" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="894">
       <c r="A894" t="s">
-        <v>423</v>
-      </c>
-      <c r="B894"/>
+        <v>424</v>
+      </c>
+      <c r="B894" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="895">
       <c r="A895" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B895" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="896">
       <c r="A896" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B896" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="897">
       <c r="A897" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B897" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="898">
       <c r="A898" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B898" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="899">
@@ -7990,75 +8277,79 @@
         <v>12</v>
       </c>
       <c r="B899" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="900">
-      <c r="A900"/>
+      <c r="A900" t="s">
+        <v>13</v>
+      </c>
       <c r="B900" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="901">
       <c r="A901" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B901" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="902">
       <c r="A902" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B902" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="903">
       <c r="A903" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B903" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="904">
       <c r="A904" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B904" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="905">
       <c r="A905" t="s">
-        <v>259</v>
-      </c>
-      <c r="B905"/>
+        <v>260</v>
+      </c>
+      <c r="B905" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="906">
       <c r="A906" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B906" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="907">
       <c r="A907" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B907" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="908">
       <c r="A908" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B908" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="909">
@@ -8066,7 +8357,7 @@
         <v>7</v>
       </c>
       <c r="B909" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="910">
@@ -8079,41 +8370,45 @@
     </row>
     <row r="911">
       <c r="A911" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B911" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="912">
       <c r="A912" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B912" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="913">
-      <c r="A913"/>
+      <c r="A913" t="s">
+        <v>13</v>
+      </c>
       <c r="B913" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="914">
       <c r="A914"/>
       <c r="B914" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="915">
       <c r="A915"/>
       <c r="B915" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="916">
       <c r="A916"/>
-      <c r="B916"/>
+      <c r="B916" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="917">
       <c r="A917"/>
@@ -8133,166 +8428,170 @@
     </row>
     <row r="921">
       <c r="A921" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B921" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="922">
       <c r="A922" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B922" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="923">
       <c r="A923" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B923" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="924">
       <c r="A924" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B924" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="925">
       <c r="A925" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B925" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="926">
       <c r="A926" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B926" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="927">
       <c r="A927" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B927" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="928">
       <c r="A928" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B928" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="929">
       <c r="A929" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B929" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="930">
       <c r="A930" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B930" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="931">
-      <c r="A931"/>
+      <c r="A931" t="s">
+        <v>13</v>
+      </c>
       <c r="B931" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="932">
       <c r="A932" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B932" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="933">
       <c r="A933" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B933" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="934">
       <c r="A934" t="s">
-        <v>54</v>
-      </c>
-      <c r="B934"/>
+        <v>55</v>
+      </c>
+      <c r="B934" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="935">
       <c r="A935" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B935" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="936">
       <c r="A936" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B936" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="937">
       <c r="A937" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B937" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="938">
       <c r="A938" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B938" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="939">
       <c r="A939" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B939" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="940">
       <c r="A940" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B940" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="941">
       <c r="A941" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B941" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="942">
@@ -8300,18 +8599,22 @@
         <v>12</v>
       </c>
       <c r="B942" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="943">
-      <c r="A943"/>
+      <c r="A943" t="s">
+        <v>13</v>
+      </c>
       <c r="B943" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="944">
       <c r="A944"/>
-      <c r="B944"/>
+      <c r="B944" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="945">
       <c r="A945"/>
@@ -8403,48 +8706,50 @@
     </row>
     <row r="967">
       <c r="A967" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B967" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="968">
       <c r="A968" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B968" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="969">
       <c r="A969" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B969" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="970">
       <c r="A970" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B970" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="971">
       <c r="A971" t="s">
-        <v>402</v>
-      </c>
-      <c r="B971"/>
+        <v>403</v>
+      </c>
+      <c r="B971" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="972">
       <c r="A972" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B972" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="973">
@@ -8452,279 +8757,299 @@
         <v>7</v>
       </c>
       <c r="B973" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="974">
-      <c r="A974"/>
+      <c r="A974" t="s">
+        <v>13</v>
+      </c>
       <c r="B974" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="975">
       <c r="A975" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B975" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="976">
       <c r="A976" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B976" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="977">
       <c r="A977" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B977" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="978">
       <c r="A978" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B978" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="979">
       <c r="A979" t="s">
-        <v>340</v>
-      </c>
-      <c r="B979"/>
+        <v>341</v>
+      </c>
+      <c r="B979" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="980">
       <c r="A980" t="s">
         <v>8</v>
       </c>
       <c r="B980" s="1" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="981">
       <c r="A981" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B981" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="982">
       <c r="A982" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B982" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="983">
-      <c r="A983"/>
-      <c r="B983"/>
+      <c r="A983" t="s">
+        <v>13</v>
+      </c>
+      <c r="B983" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="984">
       <c r="A984" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B984" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="985">
       <c r="A985" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B985" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="986">
       <c r="A986" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B986" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="987">
       <c r="A987" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B987" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="988">
       <c r="A988" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B988" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="989">
       <c r="A989" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B989" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="990">
       <c r="A990" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B990" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="991">
       <c r="A991" t="s">
-        <v>92</v>
-      </c>
-      <c r="B991"/>
+        <v>93</v>
+      </c>
+      <c r="B991" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="992">
-      <c r="A992"/>
+      <c r="A992" t="s">
+        <v>13</v>
+      </c>
       <c r="B992" s="1" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="993">
       <c r="A993" s="1" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B993" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="994">
       <c r="A994" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B994" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="995">
       <c r="A995" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B995" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="996">
       <c r="A996" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B996" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="997">
       <c r="A997" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B997" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="998">
       <c r="A998" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B998" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="999">
       <c r="A999" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B999" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="1000">
-      <c r="A1000"/>
+      <c r="A1000" t="s">
+        <v>13</v>
+      </c>
       <c r="B1000" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1001">
       <c r="A1001" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B1001" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="1002">
       <c r="A1002" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B1002" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="1003">
       <c r="A1003" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B1003" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="1004">
-      <c r="A1004"/>
+      <c r="A1004" t="s">
+        <v>13</v>
+      </c>
       <c r="B1004" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1005">
       <c r="A1005" s="1" t="s">
-        <v>530</v>
-      </c>
-      <c r="B1005"/>
+        <v>531</v>
+      </c>
+      <c r="B1005" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1006">
       <c r="A1006" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B1006"/>
     </row>
     <row r="1007">
       <c r="A1007" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B1007"/>
     </row>
     <row r="1008">
       <c r="A1008" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B1008"/>
     </row>
     <row r="1009">
       <c r="A1009" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B1009"/>
     </row>
     <row r="1010">
       <c r="A1010" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B1010"/>
     </row>
     <row r="1011">
-      <c r="A1011"/>
+      <c r="A1011" t="s">
+        <v>13</v>
+      </c>
       <c r="B1011"/>
     </row>
     <row r="1012">
@@ -8733,1013 +9058,1863 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A1">
-    <cfRule type="expression" dxfId="0" priority="202">
+    <cfRule type="expression" dxfId="0" priority="372">
       <formula>A1&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:A2">
-    <cfRule type="expression" dxfId="0" priority="201">
+    <cfRule type="expression" dxfId="0" priority="371">
       <formula>A2&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A10:A10">
-    <cfRule type="expression" dxfId="0" priority="200">
+    <cfRule type="expression" dxfId="0" priority="370">
       <formula>A10&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A20:A20">
-    <cfRule type="expression" dxfId="0" priority="199">
+    <cfRule type="expression" dxfId="0" priority="369">
       <formula>A20&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27:A27">
-    <cfRule type="expression" dxfId="0" priority="198">
+    <cfRule type="expression" dxfId="0" priority="368">
       <formula>A27&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A47:A47">
-    <cfRule type="expression" dxfId="0" priority="197">
+    <cfRule type="expression" dxfId="0" priority="367">
       <formula>A47&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A48:A48">
-    <cfRule type="expression" dxfId="0" priority="196">
+    <cfRule type="expression" dxfId="0" priority="366">
       <formula>A48&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A60:A60">
-    <cfRule type="expression" dxfId="0" priority="195">
+    <cfRule type="expression" dxfId="0" priority="365">
       <formula>A60&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A67:A67">
-    <cfRule type="expression" dxfId="0" priority="194">
+    <cfRule type="expression" dxfId="0" priority="364">
       <formula>A67&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A78:A78">
-    <cfRule type="expression" dxfId="0" priority="193">
+    <cfRule type="expression" dxfId="0" priority="363">
       <formula>A78&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A93:A93">
-    <cfRule type="expression" dxfId="0" priority="192">
+    <cfRule type="expression" dxfId="0" priority="362">
       <formula>A93&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A94:A94">
-    <cfRule type="expression" dxfId="0" priority="191">
+    <cfRule type="expression" dxfId="0" priority="361">
       <formula>A94&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A103:A103">
-    <cfRule type="expression" dxfId="0" priority="190">
+    <cfRule type="expression" dxfId="0" priority="360">
       <formula>A103&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A109:A109">
-    <cfRule type="expression" dxfId="0" priority="189">
+    <cfRule type="expression" dxfId="0" priority="359">
       <formula>A109&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A117:A117">
-    <cfRule type="expression" dxfId="0" priority="188">
+    <cfRule type="expression" dxfId="0" priority="358">
       <formula>A117&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A125:A125">
-    <cfRule type="expression" dxfId="0" priority="187">
+    <cfRule type="expression" dxfId="0" priority="357">
       <formula>A125&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A139:A139">
-    <cfRule type="expression" dxfId="0" priority="186">
+    <cfRule type="expression" dxfId="0" priority="356">
       <formula>A139&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A140:A140">
-    <cfRule type="expression" dxfId="0" priority="185">
+    <cfRule type="expression" dxfId="0" priority="355">
       <formula>A140&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A144:A144">
-    <cfRule type="expression" dxfId="0" priority="184">
+    <cfRule type="expression" dxfId="0" priority="354">
       <formula>A144&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A185:A185">
-    <cfRule type="expression" dxfId="1" priority="183">
+    <cfRule type="expression" dxfId="1" priority="353">
       <formula>A185&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A186:A186">
-    <cfRule type="expression" dxfId="1" priority="182">
+    <cfRule type="expression" dxfId="1" priority="352">
       <formula>A186&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A194:A194">
-    <cfRule type="expression" dxfId="1" priority="181">
+    <cfRule type="expression" dxfId="1" priority="351">
       <formula>A194&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A205:A205">
-    <cfRule type="expression" dxfId="1" priority="180">
+    <cfRule type="expression" dxfId="1" priority="350">
       <formula>A205&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A214:A214">
-    <cfRule type="expression" dxfId="1" priority="179">
+    <cfRule type="expression" dxfId="1" priority="349">
       <formula>A214&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A231:A231">
-    <cfRule type="expression" dxfId="1" priority="178">
+    <cfRule type="expression" dxfId="1" priority="348">
       <formula>A231&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A232:A232">
-    <cfRule type="expression" dxfId="1" priority="177">
+    <cfRule type="expression" dxfId="1" priority="347">
       <formula>A232&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A242:A242">
-    <cfRule type="expression" dxfId="1" priority="176">
+    <cfRule type="expression" dxfId="1" priority="346">
       <formula>A242&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A260:A260">
-    <cfRule type="expression" dxfId="1" priority="175">
+    <cfRule type="expression" dxfId="1" priority="345">
       <formula>A260&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A277:A277">
-    <cfRule type="expression" dxfId="1" priority="174">
+    <cfRule type="expression" dxfId="1" priority="344">
       <formula>A277&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A278:A278">
-    <cfRule type="expression" dxfId="1" priority="173">
+    <cfRule type="expression" dxfId="1" priority="343">
       <formula>A278&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A298:A298">
-    <cfRule type="expression" dxfId="1" priority="172">
+    <cfRule type="expression" dxfId="1" priority="342">
       <formula>A298&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A308:A308">
-    <cfRule type="expression" dxfId="1" priority="171">
+    <cfRule type="expression" dxfId="1" priority="341">
       <formula>A308&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A313:A313">
-    <cfRule type="expression" dxfId="1" priority="170">
+    <cfRule type="expression" dxfId="1" priority="340">
       <formula>A313&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A323:A323">
-    <cfRule type="expression" dxfId="1" priority="169">
+    <cfRule type="expression" dxfId="1" priority="339">
       <formula>A323&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A324:A324">
-    <cfRule type="expression" dxfId="1" priority="168">
+    <cfRule type="expression" dxfId="1" priority="338">
       <formula>A324&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A328:A328">
-    <cfRule type="expression" dxfId="1" priority="167">
+    <cfRule type="expression" dxfId="1" priority="337">
       <formula>A328&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A369:A369">
-    <cfRule type="expression" dxfId="2" priority="166">
+    <cfRule type="expression" dxfId="2" priority="336">
       <formula>A369&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A370:A370">
-    <cfRule type="expression" dxfId="2" priority="165">
+    <cfRule type="expression" dxfId="2" priority="335">
       <formula>A370&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A380:A380">
-    <cfRule type="expression" dxfId="2" priority="164">
+    <cfRule type="expression" dxfId="2" priority="334">
       <formula>A380&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A392:A392">
-    <cfRule type="expression" dxfId="2" priority="163">
+    <cfRule type="expression" dxfId="2" priority="333">
       <formula>A392&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A415:A415">
-    <cfRule type="expression" dxfId="2" priority="162">
+    <cfRule type="expression" dxfId="2" priority="332">
       <formula>A415&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A416:A416">
-    <cfRule type="expression" dxfId="2" priority="161">
+    <cfRule type="expression" dxfId="2" priority="331">
       <formula>A416&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A427:A427">
-    <cfRule type="expression" dxfId="2" priority="160">
+    <cfRule type="expression" dxfId="2" priority="330">
       <formula>A427&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A439:A439">
-    <cfRule type="expression" dxfId="2" priority="159">
+    <cfRule type="expression" dxfId="2" priority="329">
       <formula>A439&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A449:A449">
-    <cfRule type="expression" dxfId="2" priority="158">
+    <cfRule type="expression" dxfId="2" priority="328">
       <formula>A449&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A461:A461">
-    <cfRule type="expression" dxfId="2" priority="157">
+    <cfRule type="expression" dxfId="2" priority="327">
       <formula>A461&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A462:A462">
-    <cfRule type="expression" dxfId="2" priority="156">
+    <cfRule type="expression" dxfId="2" priority="326">
       <formula>A462&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A472:A472">
-    <cfRule type="expression" dxfId="2" priority="155">
+    <cfRule type="expression" dxfId="2" priority="325">
       <formula>A472&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A482:A482">
-    <cfRule type="expression" dxfId="2" priority="154">
+    <cfRule type="expression" dxfId="2" priority="324">
       <formula>A482&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A492:A492">
-    <cfRule type="expression" dxfId="2" priority="153">
+    <cfRule type="expression" dxfId="2" priority="323">
       <formula>A492&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A507:A507">
-    <cfRule type="expression" dxfId="2" priority="152">
+    <cfRule type="expression" dxfId="2" priority="322">
       <formula>A507&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A508:A508">
-    <cfRule type="expression" dxfId="2" priority="151">
+    <cfRule type="expression" dxfId="2" priority="321">
       <formula>A508&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A516:A516">
-    <cfRule type="expression" dxfId="2" priority="150">
+    <cfRule type="expression" dxfId="2" priority="320">
       <formula>A516&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A553:A553">
-    <cfRule type="expression" dxfId="3" priority="149">
+    <cfRule type="expression" dxfId="3" priority="319">
       <formula>A553&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A554:A554">
-    <cfRule type="expression" dxfId="3" priority="148">
+    <cfRule type="expression" dxfId="3" priority="318">
       <formula>A554&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A558:A558">
-    <cfRule type="expression" dxfId="3" priority="147">
+    <cfRule type="expression" dxfId="3" priority="317">
       <formula>A558&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A566:A566">
-    <cfRule type="expression" dxfId="3" priority="146">
+    <cfRule type="expression" dxfId="3" priority="316">
       <formula>A566&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A599:A599">
-    <cfRule type="expression" dxfId="4" priority="145">
+    <cfRule type="expression" dxfId="4" priority="315">
       <formula>A599&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A600:A600">
-    <cfRule type="expression" dxfId="4" priority="144">
+    <cfRule type="expression" dxfId="4" priority="314">
       <formula>A600&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A608:A608">
-    <cfRule type="expression" dxfId="4" priority="143">
+    <cfRule type="expression" dxfId="4" priority="313">
       <formula>A608&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A617:A617">
-    <cfRule type="expression" dxfId="4" priority="142">
+    <cfRule type="expression" dxfId="4" priority="312">
       <formula>A617&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A626:A626">
-    <cfRule type="expression" dxfId="4" priority="141">
+    <cfRule type="expression" dxfId="4" priority="311">
       <formula>A626&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A631:A631">
-    <cfRule type="expression" dxfId="4" priority="140">
+    <cfRule type="expression" dxfId="4" priority="310">
       <formula>A631&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A645:A645">
-    <cfRule type="expression" dxfId="4" priority="139">
+    <cfRule type="expression" dxfId="4" priority="309">
       <formula>A645&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A646:A646">
-    <cfRule type="expression" dxfId="4" priority="138">
+    <cfRule type="expression" dxfId="4" priority="308">
       <formula>A646&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A653:A653">
-    <cfRule type="expression" dxfId="4" priority="137">
+    <cfRule type="expression" dxfId="4" priority="307">
       <formula>A653&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A661:A661">
-    <cfRule type="expression" dxfId="4" priority="136">
+    <cfRule type="expression" dxfId="4" priority="306">
       <formula>A661&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A668:A668">
-    <cfRule type="expression" dxfId="4" priority="135">
+    <cfRule type="expression" dxfId="4" priority="305">
       <formula>A668&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A672:A672">
-    <cfRule type="expression" dxfId="4" priority="134">
+    <cfRule type="expression" dxfId="4" priority="304">
       <formula>A672&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A680:A680">
-    <cfRule type="expression" dxfId="4" priority="133">
+    <cfRule type="expression" dxfId="4" priority="303">
       <formula>A680&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A684:A684">
-    <cfRule type="expression" dxfId="4" priority="132">
+    <cfRule type="expression" dxfId="4" priority="302">
       <formula>A684&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A691:A691">
-    <cfRule type="expression" dxfId="4" priority="131">
+    <cfRule type="expression" dxfId="4" priority="301">
       <formula>A691&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A692:A692">
-    <cfRule type="expression" dxfId="4" priority="130">
+    <cfRule type="expression" dxfId="4" priority="300">
       <formula>A692&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A699:A699">
-    <cfRule type="expression" dxfId="4" priority="129">
+    <cfRule type="expression" dxfId="4" priority="299">
       <formula>A699&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A707:A707">
-    <cfRule type="expression" dxfId="4" priority="128">
+    <cfRule type="expression" dxfId="4" priority="298">
       <formula>A707&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A737:A737">
-    <cfRule type="expression" dxfId="5" priority="127">
+    <cfRule type="expression" dxfId="5" priority="297">
       <formula>A737&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A738:A738">
-    <cfRule type="expression" dxfId="5" priority="126">
+    <cfRule type="expression" dxfId="5" priority="296">
       <formula>A738&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A748:A748">
-    <cfRule type="expression" dxfId="5" priority="125">
+    <cfRule type="expression" dxfId="5" priority="295">
       <formula>A748&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A761:A761">
-    <cfRule type="expression" dxfId="5" priority="124">
+    <cfRule type="expression" dxfId="5" priority="294">
       <formula>A761&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A770:A770">
-    <cfRule type="expression" dxfId="5" priority="123">
+    <cfRule type="expression" dxfId="5" priority="293">
       <formula>A770&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A783:A783">
-    <cfRule type="expression" dxfId="5" priority="122">
+    <cfRule type="expression" dxfId="5" priority="292">
       <formula>A783&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A784:A784">
-    <cfRule type="expression" dxfId="5" priority="121">
+    <cfRule type="expression" dxfId="5" priority="291">
       <formula>A784&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A795:A795">
-    <cfRule type="expression" dxfId="5" priority="120">
+    <cfRule type="expression" dxfId="5" priority="290">
       <formula>A795&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A804:A804">
-    <cfRule type="expression" dxfId="5" priority="119">
+    <cfRule type="expression" dxfId="5" priority="289">
       <formula>A804&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A813:A813">
-    <cfRule type="expression" dxfId="5" priority="118">
+    <cfRule type="expression" dxfId="5" priority="288">
       <formula>A813&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A829:A829">
-    <cfRule type="expression" dxfId="5" priority="117">
+    <cfRule type="expression" dxfId="5" priority="287">
       <formula>A829&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A830:A830">
-    <cfRule type="expression" dxfId="5" priority="116">
+    <cfRule type="expression" dxfId="5" priority="286">
       <formula>A830&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A840:A840">
-    <cfRule type="expression" dxfId="5" priority="115">
+    <cfRule type="expression" dxfId="5" priority="285">
       <formula>A840&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A853:A853">
-    <cfRule type="expression" dxfId="5" priority="114">
+    <cfRule type="expression" dxfId="5" priority="284">
       <formula>A853&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A875:A875">
-    <cfRule type="expression" dxfId="6" priority="113">
+    <cfRule type="expression" dxfId="6" priority="283">
       <formula>A875&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A876:A876">
-    <cfRule type="expression" dxfId="6" priority="112">
+    <cfRule type="expression" dxfId="6" priority="282">
       <formula>A876&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A886:A886">
-    <cfRule type="expression" dxfId="6" priority="111">
+    <cfRule type="expression" dxfId="6" priority="281">
       <formula>A886&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A892:A892">
-    <cfRule type="expression" dxfId="6" priority="110">
+    <cfRule type="expression" dxfId="6" priority="280">
       <formula>A892&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A901:A901">
-    <cfRule type="expression" dxfId="6" priority="109">
+    <cfRule type="expression" dxfId="6" priority="279">
       <formula>A901&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A921:A921">
-    <cfRule type="expression" dxfId="6" priority="108">
+    <cfRule type="expression" dxfId="6" priority="278">
       <formula>A921&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A922:A922">
-    <cfRule type="expression" dxfId="6" priority="107">
+    <cfRule type="expression" dxfId="6" priority="277">
       <formula>A922&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A932:A932">
-    <cfRule type="expression" dxfId="6" priority="106">
+    <cfRule type="expression" dxfId="6" priority="276">
       <formula>A932&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A967:A967">
-    <cfRule type="expression" dxfId="7" priority="105">
+    <cfRule type="expression" dxfId="7" priority="275">
       <formula>A967&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A968:A968">
-    <cfRule type="expression" dxfId="7" priority="104">
+    <cfRule type="expression" dxfId="7" priority="274">
       <formula>A968&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A975:A975">
-    <cfRule type="expression" dxfId="7" priority="103">
+    <cfRule type="expression" dxfId="7" priority="273">
       <formula>A975&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A984:A984">
-    <cfRule type="expression" dxfId="7" priority="102">
+    <cfRule type="expression" dxfId="7" priority="272">
       <formula>A984&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A993:A993">
-    <cfRule type="expression" dxfId="7" priority="101">
+    <cfRule type="expression" dxfId="7" priority="271">
       <formula>A993&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1001:A1001">
-    <cfRule type="expression" dxfId="7" priority="100">
+    <cfRule type="expression" dxfId="7" priority="270">
       <formula>A1001&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1005:A1005">
-    <cfRule type="expression" dxfId="7" priority="99">
+    <cfRule type="expression" dxfId="7" priority="269">
       <formula>A1005&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B1">
-    <cfRule type="expression" dxfId="0" priority="98">
+    <cfRule type="expression" dxfId="0" priority="268">
       <formula>B1&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:B2">
-    <cfRule type="expression" dxfId="0" priority="97">
+    <cfRule type="expression" dxfId="0" priority="267">
       <formula>B2&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:B14">
-    <cfRule type="expression" dxfId="0" priority="96">
+    <cfRule type="expression" dxfId="0" priority="266">
       <formula>B14&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32:B32">
-    <cfRule type="expression" dxfId="0" priority="95">
+    <cfRule type="expression" dxfId="0" priority="265">
       <formula>B32&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B47:B47">
-    <cfRule type="expression" dxfId="0" priority="94">
+    <cfRule type="expression" dxfId="0" priority="264">
       <formula>B47&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B48:B48">
-    <cfRule type="expression" dxfId="0" priority="93">
+    <cfRule type="expression" dxfId="0" priority="263">
       <formula>B48&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B64:B64">
-    <cfRule type="expression" dxfId="0" priority="92">
+    <cfRule type="expression" dxfId="0" priority="262">
       <formula>B64&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B76:B76">
-    <cfRule type="expression" dxfId="0" priority="91">
+    <cfRule type="expression" dxfId="0" priority="261">
       <formula>B76&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B93:B93">
-    <cfRule type="expression" dxfId="0" priority="90">
+    <cfRule type="expression" dxfId="0" priority="260">
       <formula>B93&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B94:B94">
-    <cfRule type="expression" dxfId="0" priority="89">
+    <cfRule type="expression" dxfId="0" priority="259">
       <formula>B94&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B105:B105">
-    <cfRule type="expression" dxfId="0" priority="88">
+    <cfRule type="expression" dxfId="0" priority="258">
       <formula>B105&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B118:B118">
-    <cfRule type="expression" dxfId="0" priority="87">
+    <cfRule type="expression" dxfId="0" priority="257">
       <formula>B118&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B129:B129">
-    <cfRule type="expression" dxfId="0" priority="86">
+    <cfRule type="expression" dxfId="0" priority="256">
       <formula>B129&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B139:B139">
-    <cfRule type="expression" dxfId="0" priority="85">
+    <cfRule type="expression" dxfId="0" priority="255">
       <formula>B139&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B140:B140">
-    <cfRule type="expression" dxfId="0" priority="84">
+    <cfRule type="expression" dxfId="0" priority="254">
       <formula>B140&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B185:B185">
-    <cfRule type="expression" dxfId="1" priority="83">
+    <cfRule type="expression" dxfId="1" priority="253">
       <formula>B185&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B186:B186">
-    <cfRule type="expression" dxfId="1" priority="82">
+    <cfRule type="expression" dxfId="1" priority="252">
       <formula>B186&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B195:B195">
-    <cfRule type="expression" dxfId="1" priority="81">
+    <cfRule type="expression" dxfId="1" priority="251">
       <formula>B195&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B205:B205">
-    <cfRule type="expression" dxfId="1" priority="80">
+    <cfRule type="expression" dxfId="1" priority="250">
       <formula>B205&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B214:B214">
-    <cfRule type="expression" dxfId="1" priority="79">
+    <cfRule type="expression" dxfId="1" priority="249">
       <formula>B214&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B231:B231">
-    <cfRule type="expression" dxfId="1" priority="78">
+    <cfRule type="expression" dxfId="1" priority="248">
       <formula>B231&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B232:B232">
-    <cfRule type="expression" dxfId="1" priority="77">
+    <cfRule type="expression" dxfId="1" priority="247">
       <formula>B232&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B242:B242">
-    <cfRule type="expression" dxfId="1" priority="76">
+    <cfRule type="expression" dxfId="1" priority="246">
       <formula>B242&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B250:B250">
-    <cfRule type="expression" dxfId="1" priority="75">
+    <cfRule type="expression" dxfId="1" priority="245">
       <formula>B250&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B277:B277">
-    <cfRule type="expression" dxfId="1" priority="74">
+    <cfRule type="expression" dxfId="1" priority="244">
       <formula>B277&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B278:B278">
-    <cfRule type="expression" dxfId="1" priority="73">
+    <cfRule type="expression" dxfId="1" priority="243">
       <formula>B278&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B290:B290">
-    <cfRule type="expression" dxfId="1" priority="72">
+    <cfRule type="expression" dxfId="1" priority="242">
       <formula>B290&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B301:B301">
-    <cfRule type="expression" dxfId="1" priority="71">
+    <cfRule type="expression" dxfId="1" priority="241">
       <formula>B301&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B305:B305">
-    <cfRule type="expression" dxfId="1" priority="70">
+    <cfRule type="expression" dxfId="1" priority="240">
       <formula>B305&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B315:B315">
-    <cfRule type="expression" dxfId="1" priority="69">
+    <cfRule type="expression" dxfId="1" priority="239">
       <formula>B315&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B323:B323">
-    <cfRule type="expression" dxfId="1" priority="68">
+    <cfRule type="expression" dxfId="1" priority="238">
       <formula>B323&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B324:B324">
-    <cfRule type="expression" dxfId="1" priority="67">
+    <cfRule type="expression" dxfId="1" priority="237">
       <formula>B324&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B328:B328">
-    <cfRule type="expression" dxfId="1" priority="66">
+    <cfRule type="expression" dxfId="1" priority="236">
       <formula>B328&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B369:B369">
-    <cfRule type="expression" dxfId="2" priority="65">
+    <cfRule type="expression" dxfId="2" priority="235">
       <formula>B369&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B370:B370">
-    <cfRule type="expression" dxfId="2" priority="64">
+    <cfRule type="expression" dxfId="2" priority="234">
       <formula>B370&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B381:B381">
-    <cfRule type="expression" dxfId="2" priority="63">
+    <cfRule type="expression" dxfId="2" priority="233">
       <formula>B381&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B393:B393">
-    <cfRule type="expression" dxfId="2" priority="62">
+    <cfRule type="expression" dxfId="2" priority="232">
       <formula>B393&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B415:B415">
-    <cfRule type="expression" dxfId="2" priority="61">
+    <cfRule type="expression" dxfId="2" priority="231">
       <formula>B415&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B416:B416">
-    <cfRule type="expression" dxfId="2" priority="60">
+    <cfRule type="expression" dxfId="2" priority="230">
       <formula>B416&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B428:B428">
-    <cfRule type="expression" dxfId="2" priority="59">
+    <cfRule type="expression" dxfId="2" priority="229">
       <formula>B428&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B440:B440">
-    <cfRule type="expression" dxfId="2" priority="58">
+    <cfRule type="expression" dxfId="2" priority="228">
       <formula>B440&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B449:B449">
-    <cfRule type="expression" dxfId="2" priority="57">
+    <cfRule type="expression" dxfId="2" priority="227">
       <formula>B449&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B461:B461">
-    <cfRule type="expression" dxfId="2" priority="56">
+    <cfRule type="expression" dxfId="2" priority="226">
       <formula>B461&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B462:B462">
-    <cfRule type="expression" dxfId="2" priority="55">
+    <cfRule type="expression" dxfId="2" priority="225">
       <formula>B462&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B469:B469">
-    <cfRule type="expression" dxfId="2" priority="54">
+    <cfRule type="expression" dxfId="2" priority="224">
       <formula>B469&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B480:B480">
-    <cfRule type="expression" dxfId="2" priority="53">
+    <cfRule type="expression" dxfId="2" priority="223">
       <formula>B480&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B491:B491">
-    <cfRule type="expression" dxfId="2" priority="52">
+    <cfRule type="expression" dxfId="2" priority="222">
       <formula>B491&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B496:B496">
-    <cfRule type="expression" dxfId="2" priority="51">
+    <cfRule type="expression" dxfId="2" priority="221">
       <formula>B496&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B507:B507">
-    <cfRule type="expression" dxfId="2" priority="50">
+    <cfRule type="expression" dxfId="2" priority="220">
       <formula>B507&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B508:B508">
-    <cfRule type="expression" dxfId="2" priority="49">
+    <cfRule type="expression" dxfId="2" priority="219">
       <formula>B508&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B553:B553">
-    <cfRule type="expression" dxfId="3" priority="48">
+    <cfRule type="expression" dxfId="3" priority="218">
       <formula>B553&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B554:B554">
-    <cfRule type="expression" dxfId="3" priority="47">
+    <cfRule type="expression" dxfId="3" priority="217">
       <formula>B554&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B560:B560">
-    <cfRule type="expression" dxfId="3" priority="46">
+    <cfRule type="expression" dxfId="3" priority="216">
       <formula>B560&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B570:B570">
-    <cfRule type="expression" dxfId="3" priority="45">
+    <cfRule type="expression" dxfId="3" priority="215">
       <formula>B570&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B599:B599">
-    <cfRule type="expression" dxfId="4" priority="44">
+    <cfRule type="expression" dxfId="4" priority="214">
       <formula>B599&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B600:B600">
-    <cfRule type="expression" dxfId="4" priority="43">
+    <cfRule type="expression" dxfId="4" priority="213">
       <formula>B600&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B608:B608">
-    <cfRule type="expression" dxfId="4" priority="42">
+    <cfRule type="expression" dxfId="4" priority="212">
       <formula>B608&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B615:B615">
-    <cfRule type="expression" dxfId="4" priority="41">
+    <cfRule type="expression" dxfId="4" priority="211">
       <formula>B615&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B624:B624">
-    <cfRule type="expression" dxfId="4" priority="40">
+    <cfRule type="expression" dxfId="4" priority="210">
       <formula>B624&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B632:B632">
-    <cfRule type="expression" dxfId="4" priority="39">
+    <cfRule type="expression" dxfId="4" priority="209">
       <formula>B632&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B645:B645">
-    <cfRule type="expression" dxfId="4" priority="38">
+    <cfRule type="expression" dxfId="4" priority="208">
       <formula>B645&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B646:B646">
-    <cfRule type="expression" dxfId="4" priority="37">
+    <cfRule type="expression" dxfId="4" priority="207">
       <formula>B646&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B654:B654">
-    <cfRule type="expression" dxfId="4" priority="36">
+    <cfRule type="expression" dxfId="4" priority="206">
       <formula>B654&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B663:B663">
-    <cfRule type="expression" dxfId="4" priority="35">
+    <cfRule type="expression" dxfId="4" priority="205">
       <formula>B663&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B670:B670">
-    <cfRule type="expression" dxfId="4" priority="34">
+    <cfRule type="expression" dxfId="4" priority="204">
       <formula>B670&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B679:B679">
-    <cfRule type="expression" dxfId="4" priority="33">
+    <cfRule type="expression" dxfId="4" priority="203">
       <formula>B679&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B683:B683">
-    <cfRule type="expression" dxfId="4" priority="32">
+    <cfRule type="expression" dxfId="4" priority="202">
       <formula>B683&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B691:B691">
-    <cfRule type="expression" dxfId="4" priority="31">
+    <cfRule type="expression" dxfId="4" priority="201">
       <formula>B691&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B692:B692">
-    <cfRule type="expression" dxfId="4" priority="30">
+    <cfRule type="expression" dxfId="4" priority="200">
       <formula>B692&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B702:B702">
-    <cfRule type="expression" dxfId="4" priority="29">
+    <cfRule type="expression" dxfId="4" priority="199">
       <formula>B702&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B706:B706">
-    <cfRule type="expression" dxfId="4" priority="28">
+    <cfRule type="expression" dxfId="4" priority="198">
       <formula>B706&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B737:B737">
-    <cfRule type="expression" dxfId="5" priority="27">
+    <cfRule type="expression" dxfId="5" priority="197">
       <formula>B737&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B738:B738">
-    <cfRule type="expression" dxfId="5" priority="26">
+    <cfRule type="expression" dxfId="5" priority="196">
       <formula>B738&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B747:B747">
-    <cfRule type="expression" dxfId="5" priority="25">
+    <cfRule type="expression" dxfId="5" priority="195">
       <formula>B747&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B757:B757">
-    <cfRule type="expression" dxfId="5" priority="24">
+    <cfRule type="expression" dxfId="5" priority="194">
       <formula>B757&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B766:B766">
-    <cfRule type="expression" dxfId="5" priority="23">
+    <cfRule type="expression" dxfId="5" priority="193">
       <formula>B766&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B783:B783">
-    <cfRule type="expression" dxfId="5" priority="22">
+    <cfRule type="expression" dxfId="5" priority="192">
       <formula>B783&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B784:B784">
-    <cfRule type="expression" dxfId="5" priority="21">
+    <cfRule type="expression" dxfId="5" priority="191">
       <formula>B784&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B794:B794">
-    <cfRule type="expression" dxfId="5" priority="20">
+    <cfRule type="expression" dxfId="5" priority="190">
       <formula>B794&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B804:B804">
-    <cfRule type="expression" dxfId="5" priority="19">
+    <cfRule type="expression" dxfId="5" priority="189">
       <formula>B804&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B811:B811">
-    <cfRule type="expression" dxfId="5" priority="18">
+    <cfRule type="expression" dxfId="5" priority="188">
       <formula>B811&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B829:B829">
-    <cfRule type="expression" dxfId="5" priority="17">
+    <cfRule type="expression" dxfId="5" priority="187">
       <formula>B829&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B830:B830">
-    <cfRule type="expression" dxfId="5" priority="16">
+    <cfRule type="expression" dxfId="5" priority="186">
       <formula>B830&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B840:B840">
-    <cfRule type="expression" dxfId="5" priority="15">
+    <cfRule type="expression" dxfId="5" priority="185">
       <formula>B840&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B875:B875">
-    <cfRule type="expression" dxfId="6" priority="14">
+    <cfRule type="expression" dxfId="6" priority="184">
       <formula>B875&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B876:B876">
-    <cfRule type="expression" dxfId="6" priority="13">
+    <cfRule type="expression" dxfId="6" priority="183">
       <formula>B876&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B884:B884">
-    <cfRule type="expression" dxfId="6" priority="12">
+    <cfRule type="expression" dxfId="6" priority="182">
       <formula>B884&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B895:B895">
-    <cfRule type="expression" dxfId="6" priority="11">
+    <cfRule type="expression" dxfId="6" priority="181">
       <formula>B895&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B906:B906">
-    <cfRule type="expression" dxfId="6" priority="10">
+    <cfRule type="expression" dxfId="6" priority="180">
       <formula>B906&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B921:B921">
-    <cfRule type="expression" dxfId="6" priority="9">
+    <cfRule type="expression" dxfId="6" priority="179">
       <formula>B921&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B922:B922">
-    <cfRule type="expression" dxfId="6" priority="8">
+    <cfRule type="expression" dxfId="6" priority="178">
       <formula>B922&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B935:B935">
-    <cfRule type="expression" dxfId="6" priority="7">
+    <cfRule type="expression" dxfId="6" priority="177">
       <formula>B935&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B967:B967">
-    <cfRule type="expression" dxfId="7" priority="6">
+    <cfRule type="expression" dxfId="7" priority="176">
       <formula>B967&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B968:B968">
-    <cfRule type="expression" dxfId="7" priority="5">
+    <cfRule type="expression" dxfId="7" priority="175">
       <formula>B968&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B972:B972">
-    <cfRule type="expression" dxfId="7" priority="4">
+    <cfRule type="expression" dxfId="7" priority="174">
       <formula>B972&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B980:B980">
-    <cfRule type="expression" dxfId="7" priority="3">
+    <cfRule type="expression" dxfId="7" priority="173">
       <formula>B980&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B984:B984">
-    <cfRule type="expression" dxfId="7" priority="2">
+    <cfRule type="expression" dxfId="7" priority="172">
       <formula>B984&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B992:B992">
-    <cfRule type="expression" dxfId="7" priority="1">
+    <cfRule type="expression" dxfId="7" priority="171">
       <formula>B992&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A8:A8">
+    <cfRule type="expression" dxfId="8" priority="170">
+      <formula>A8&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A14:A14">
+    <cfRule type="expression" dxfId="8" priority="169">
+      <formula>A14&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A17:A17">
+    <cfRule type="expression" dxfId="8" priority="168">
+      <formula>A17&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A24:A24">
+    <cfRule type="expression" dxfId="8" priority="167">
+      <formula>A24&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A31:A31">
+    <cfRule type="expression" dxfId="8" priority="166">
+      <formula>A31&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A34:A34">
+    <cfRule type="expression" dxfId="8" priority="165">
+      <formula>A34&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A36:A36">
+    <cfRule type="expression" dxfId="8" priority="164">
+      <formula>A36&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A51:A51">
+    <cfRule type="expression" dxfId="8" priority="163">
+      <formula>A51&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A54:A54">
+    <cfRule type="expression" dxfId="8" priority="162">
+      <formula>A54&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A55:A55">
+    <cfRule type="expression" dxfId="8" priority="161">
+      <formula>A55&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A83:A83">
+    <cfRule type="expression" dxfId="8" priority="160">
+      <formula>A83&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A97:A97">
+    <cfRule type="expression" dxfId="8" priority="159">
+      <formula>A97&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A148:A148">
+    <cfRule type="expression" dxfId="8" priority="158">
+      <formula>A148&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A152:A152">
+    <cfRule type="expression" dxfId="8" priority="157">
+      <formula>A152&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A198:A198">
+    <cfRule type="expression" dxfId="8" priority="156">
+      <formula>A198&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A199:A199">
+    <cfRule type="expression" dxfId="8" priority="155">
+      <formula>A199&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A201:A201">
+    <cfRule type="expression" dxfId="8" priority="154">
+      <formula>A201&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A202:A202">
+    <cfRule type="expression" dxfId="8" priority="153">
+      <formula>A202&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A203:A203">
+    <cfRule type="expression" dxfId="8" priority="152">
+      <formula>A203&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A235:A235">
+    <cfRule type="expression" dxfId="8" priority="151">
+      <formula>A235&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A238:A238">
+    <cfRule type="expression" dxfId="8" priority="150">
+      <formula>A238&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A248:A248">
+    <cfRule type="expression" dxfId="8" priority="149">
+      <formula>A248&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A251:A251">
+    <cfRule type="expression" dxfId="8" priority="148">
+      <formula>A251&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A258:A258">
+    <cfRule type="expression" dxfId="8" priority="147">
+      <formula>A258&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A264:A264">
+    <cfRule type="expression" dxfId="8" priority="146">
+      <formula>A264&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A282:A282">
+    <cfRule type="expression" dxfId="8" priority="145">
+      <formula>A282&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A283:A283">
+    <cfRule type="expression" dxfId="8" priority="144">
+      <formula>A283&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A284:A284">
+    <cfRule type="expression" dxfId="8" priority="143">
+      <formula>A284&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A296:A296">
+    <cfRule type="expression" dxfId="8" priority="142">
+      <formula>A296&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A301:A301">
+    <cfRule type="expression" dxfId="8" priority="141">
+      <formula>A301&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A303:A303">
+    <cfRule type="expression" dxfId="8" priority="140">
+      <formula>A303&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A315:A315">
+    <cfRule type="expression" dxfId="8" priority="139">
+      <formula>A315&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A317:A317">
+    <cfRule type="expression" dxfId="8" priority="138">
+      <formula>A317&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A320:A320">
+    <cfRule type="expression" dxfId="8" priority="137">
+      <formula>A320&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A333:A333">
+    <cfRule type="expression" dxfId="8" priority="136">
+      <formula>A333&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A335:A335">
+    <cfRule type="expression" dxfId="8" priority="135">
+      <formula>A335&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A336:A336">
+    <cfRule type="expression" dxfId="8" priority="134">
+      <formula>A336&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A375:A375">
+    <cfRule type="expression" dxfId="8" priority="133">
+      <formula>A375&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A376:A376">
+    <cfRule type="expression" dxfId="8" priority="132">
+      <formula>A376&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A377:A377">
+    <cfRule type="expression" dxfId="8" priority="131">
+      <formula>A377&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A386:A386">
+    <cfRule type="expression" dxfId="8" priority="130">
+      <formula>A386&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A399:A399">
+    <cfRule type="expression" dxfId="8" priority="129">
+      <formula>A399&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A422:A422">
+    <cfRule type="expression" dxfId="8" priority="128">
+      <formula>A422&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A424:A424">
+    <cfRule type="expression" dxfId="8" priority="127">
+      <formula>A424&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A425:A425">
+    <cfRule type="expression" dxfId="8" priority="126">
+      <formula>A425&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A434:A434">
+    <cfRule type="expression" dxfId="8" priority="125">
+      <formula>A434&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A436:A436">
+    <cfRule type="expression" dxfId="8" priority="124">
+      <formula>A436&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A445:A445">
+    <cfRule type="expression" dxfId="8" priority="123">
+      <formula>A445&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A447:A447">
+    <cfRule type="expression" dxfId="8" priority="122">
+      <formula>A447&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A453:A453">
+    <cfRule type="expression" dxfId="8" priority="121">
+      <formula>A453&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A458:A458">
+    <cfRule type="expression" dxfId="8" priority="120">
+      <formula>A458&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A465:A465">
+    <cfRule type="expression" dxfId="8" priority="119">
+      <formula>A465&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A467:A467">
+    <cfRule type="expression" dxfId="8" priority="118">
+      <formula>A467&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A476:A476">
+    <cfRule type="expression" dxfId="8" priority="117">
+      <formula>A476&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A477:A477">
+    <cfRule type="expression" dxfId="8" priority="116">
+      <formula>A477&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A489:A489">
+    <cfRule type="expression" dxfId="8" priority="115">
+      <formula>A489&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A496:A496">
+    <cfRule type="expression" dxfId="8" priority="114">
+      <formula>A496&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A498:A498">
+    <cfRule type="expression" dxfId="8" priority="113">
+      <formula>A498&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A499:A499">
+    <cfRule type="expression" dxfId="8" priority="112">
+      <formula>A499&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A500:A500">
+    <cfRule type="expression" dxfId="8" priority="111">
+      <formula>A500&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A510:A510">
+    <cfRule type="expression" dxfId="8" priority="110">
+      <formula>A510&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A511:A511">
+    <cfRule type="expression" dxfId="8" priority="109">
+      <formula>A511&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A513:A513">
+    <cfRule type="expression" dxfId="8" priority="108">
+      <formula>A513&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A514:A514">
+    <cfRule type="expression" dxfId="8" priority="107">
+      <formula>A514&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A658:A658">
+    <cfRule type="expression" dxfId="8" priority="106">
+      <formula>A658&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A659:A659">
+    <cfRule type="expression" dxfId="8" priority="105">
+      <formula>A659&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A674:A674">
+    <cfRule type="expression" dxfId="8" priority="104">
+      <formula>A674&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A675:A675">
+    <cfRule type="expression" dxfId="8" priority="103">
+      <formula>A675&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A676:A676">
+    <cfRule type="expression" dxfId="8" priority="102">
+      <formula>A676&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A702:A702">
+    <cfRule type="expression" dxfId="8" priority="101">
+      <formula>A702&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A704:A704">
+    <cfRule type="expression" dxfId="8" priority="100">
+      <formula>A704&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A889:A889">
+    <cfRule type="expression" dxfId="8" priority="99">
+      <formula>A889&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A895:A895">
+    <cfRule type="expression" dxfId="8" priority="98">
+      <formula>A895&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A896:A896">
+    <cfRule type="expression" dxfId="8" priority="97">
+      <formula>A896&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A899:A899">
+    <cfRule type="expression" dxfId="8" priority="96">
+      <formula>A899&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A927:A927">
+    <cfRule type="expression" dxfId="8" priority="95">
+      <formula>A927&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A935:A935">
+    <cfRule type="expression" dxfId="8" priority="94">
+      <formula>A935&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A938:A938">
+    <cfRule type="expression" dxfId="8" priority="93">
+      <formula>A938&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A942:A942">
+    <cfRule type="expression" dxfId="8" priority="92">
+      <formula>A942&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A971:A971">
+    <cfRule type="expression" dxfId="8" priority="91">
+      <formula>A971&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A981:A981">
+    <cfRule type="expression" dxfId="8" priority="90">
+      <formula>A981&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A982:A982">
+    <cfRule type="expression" dxfId="8" priority="89">
+      <formula>A982&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A997:A997">
+    <cfRule type="expression" dxfId="8" priority="88">
+      <formula>A997&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1009:A1009">
+    <cfRule type="expression" dxfId="8" priority="87">
+      <formula>A1009&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1010:A1010">
+    <cfRule type="expression" dxfId="8" priority="86">
+      <formula>A1010&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B11:B11">
+    <cfRule type="expression" dxfId="8" priority="85">
+      <formula>B11&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B20:B20">
+    <cfRule type="expression" dxfId="8" priority="84">
+      <formula>B20&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B40:B40">
+    <cfRule type="expression" dxfId="8" priority="83">
+      <formula>B40&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B58:B58">
+    <cfRule type="expression" dxfId="8" priority="82">
+      <formula>B58&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B68:B68">
+    <cfRule type="expression" dxfId="8" priority="81">
+      <formula>B68&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B72:B72">
+    <cfRule type="expression" dxfId="8" priority="80">
+      <formula>B72&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B74:B74">
+    <cfRule type="expression" dxfId="8" priority="79">
+      <formula>B74&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B80:B80">
+    <cfRule type="expression" dxfId="8" priority="78">
+      <formula>B80&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B83:B83">
+    <cfRule type="expression" dxfId="8" priority="77">
+      <formula>B83&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B85:B85">
+    <cfRule type="expression" dxfId="8" priority="76">
+      <formula>B85&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B100:B100">
+    <cfRule type="expression" dxfId="8" priority="75">
+      <formula>B100&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B103:B103">
+    <cfRule type="expression" dxfId="8" priority="74">
+      <formula>B103&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B109:B109">
+    <cfRule type="expression" dxfId="8" priority="73">
+      <formula>B109&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B110:B110">
+    <cfRule type="expression" dxfId="8" priority="72">
+      <formula>B110&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B111:B111">
+    <cfRule type="expression" dxfId="8" priority="71">
+      <formula>B111&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B116:B116">
+    <cfRule type="expression" dxfId="8" priority="70">
+      <formula>B116&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B121:B121">
+    <cfRule type="expression" dxfId="8" priority="69">
+      <formula>B121&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B134:B134">
+    <cfRule type="expression" dxfId="8" priority="68">
+      <formula>B134&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B137:B137">
+    <cfRule type="expression" dxfId="8" priority="67">
+      <formula>B137&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B198:B198">
+    <cfRule type="expression" dxfId="8" priority="66">
+      <formula>B198&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B199:B199">
+    <cfRule type="expression" dxfId="8" priority="65">
+      <formula>B199&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B200:B200">
+    <cfRule type="expression" dxfId="8" priority="64">
+      <formula>B200&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B203:B203">
+    <cfRule type="expression" dxfId="8" priority="63">
+      <formula>B203&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B210:B210">
+    <cfRule type="expression" dxfId="8" priority="62">
+      <formula>B210&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B236:B236">
+    <cfRule type="expression" dxfId="8" priority="61">
+      <formula>B236&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B237:B237">
+    <cfRule type="expression" dxfId="8" priority="60">
+      <formula>B237&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B240:B240">
+    <cfRule type="expression" dxfId="8" priority="59">
+      <formula>B240&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B254:B254">
+    <cfRule type="expression" dxfId="8" priority="58">
+      <formula>B254&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B281:B281">
+    <cfRule type="expression" dxfId="8" priority="57">
+      <formula>B281&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B283:B283">
+    <cfRule type="expression" dxfId="8" priority="56">
+      <formula>B283&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B284:B284">
+    <cfRule type="expression" dxfId="8" priority="55">
+      <formula>B284&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B288:B288">
+    <cfRule type="expression" dxfId="8" priority="54">
+      <formula>B288&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B294:B294">
+    <cfRule type="expression" dxfId="8" priority="53">
+      <formula>B294&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B307:B307">
+    <cfRule type="expression" dxfId="8" priority="52">
+      <formula>B307&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B308:B308">
+    <cfRule type="expression" dxfId="8" priority="51">
+      <formula>B308&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B309:B309">
+    <cfRule type="expression" dxfId="8" priority="50">
+      <formula>B309&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B376:B376">
+    <cfRule type="expression" dxfId="8" priority="49">
+      <formula>B376&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B385:B385">
+    <cfRule type="expression" dxfId="8" priority="48">
+      <formula>B385&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B397:B397">
+    <cfRule type="expression" dxfId="8" priority="47">
+      <formula>B397&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B398:B398">
+    <cfRule type="expression" dxfId="8" priority="46">
+      <formula>B398&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B421:B421">
+    <cfRule type="expression" dxfId="8" priority="45">
+      <formula>B421&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B424:B424">
+    <cfRule type="expression" dxfId="8" priority="44">
+      <formula>B424&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B426:B426">
+    <cfRule type="expression" dxfId="8" priority="43">
+      <formula>B426&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B436:B436">
+    <cfRule type="expression" dxfId="8" priority="42">
+      <formula>B436&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B438:B438">
+    <cfRule type="expression" dxfId="8" priority="41">
+      <formula>B438&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B445:B445">
+    <cfRule type="expression" dxfId="8" priority="40">
+      <formula>B445&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B454:B454">
+    <cfRule type="expression" dxfId="8" priority="39">
+      <formula>B454&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B456:B456">
+    <cfRule type="expression" dxfId="8" priority="38">
+      <formula>B456&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B457:B457">
+    <cfRule type="expression" dxfId="8" priority="37">
+      <formula>B457&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B466:B466">
+    <cfRule type="expression" dxfId="8" priority="36">
+      <formula>B466&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B474:B474">
+    <cfRule type="expression" dxfId="8" priority="35">
+      <formula>B474&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B484:B484">
+    <cfRule type="expression" dxfId="8" priority="34">
+      <formula>B484&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B486:B486">
+    <cfRule type="expression" dxfId="8" priority="33">
+      <formula>B486&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B498:B498">
+    <cfRule type="expression" dxfId="8" priority="32">
+      <formula>B498&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B499:B499">
+    <cfRule type="expression" dxfId="8" priority="31">
+      <formula>B499&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B500:B500">
+    <cfRule type="expression" dxfId="8" priority="30">
+      <formula>B500&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B501:B501">
+    <cfRule type="expression" dxfId="8" priority="29">
+      <formula>B501&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B502:B502">
+    <cfRule type="expression" dxfId="8" priority="28">
+      <formula>B502&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B503:B503">
+    <cfRule type="expression" dxfId="8" priority="27">
+      <formula>B503&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B604:B604">
+    <cfRule type="expression" dxfId="8" priority="26">
+      <formula>B604&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B605:B605">
+    <cfRule type="expression" dxfId="8" priority="25">
+      <formula>B605&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B612:B612">
+    <cfRule type="expression" dxfId="8" priority="24">
+      <formula>B612&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B620:B620">
+    <cfRule type="expression" dxfId="8" priority="23">
+      <formula>B620&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B628:B628">
+    <cfRule type="expression" dxfId="8" priority="22">
+      <formula>B628&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B629:B629">
+    <cfRule type="expression" dxfId="8" priority="21">
+      <formula>B629&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B649:B649">
+    <cfRule type="expression" dxfId="8" priority="20">
+      <formula>B649&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B666:B666">
+    <cfRule type="expression" dxfId="8" priority="19">
+      <formula>B666&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B674:B674">
+    <cfRule type="expression" dxfId="8" priority="18">
+      <formula>B674&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B696:B696">
+    <cfRule type="expression" dxfId="8" priority="17">
+      <formula>B696&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B887:B887">
+    <cfRule type="expression" dxfId="8" priority="16">
+      <formula>B887&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B889:B889">
+    <cfRule type="expression" dxfId="8" priority="15">
+      <formula>B889&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B891:B891">
+    <cfRule type="expression" dxfId="8" priority="14">
+      <formula>B891&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B893:B893">
+    <cfRule type="expression" dxfId="8" priority="13">
+      <formula>B893&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B900:B900">
+    <cfRule type="expression" dxfId="8" priority="12">
+      <formula>B900&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B901:B901">
+    <cfRule type="expression" dxfId="8" priority="11">
+      <formula>B901&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B903:B903">
+    <cfRule type="expression" dxfId="8" priority="10">
+      <formula>B903&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B911:B911">
+    <cfRule type="expression" dxfId="8" priority="9">
+      <formula>B911&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B913:B913">
+    <cfRule type="expression" dxfId="8" priority="8">
+      <formula>B913&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B914:B914">
+    <cfRule type="expression" dxfId="8" priority="7">
+      <formula>B914&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B929:B929">
+    <cfRule type="expression" dxfId="8" priority="6">
+      <formula>B929&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B931:B931">
+    <cfRule type="expression" dxfId="8" priority="5">
+      <formula>B931&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B932:B932">
+    <cfRule type="expression" dxfId="8" priority="4">
+      <formula>B932&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B941:B941">
+    <cfRule type="expression" dxfId="8" priority="3">
+      <formula>B941&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B943:B943">
+    <cfRule type="expression" dxfId="8" priority="2">
+      <formula>B943&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1000:B1000">
+    <cfRule type="expression" dxfId="8" priority="1">
+      <formula>B1000&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
